--- a/server/templates/gip-template.xlsx
+++ b/server/templates/gip-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\GO-PESO-GIP\GUWIP DATA FORM TALLY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\GO-PESO-GIP\Website\LGU_PESD_WEBSITE\PLGU-PESD-system\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81586CF0-7892-4DF8-8805-155F8332C4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD866F2-408D-410A-B895-0447B8139C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8DF5B536-FA94-48BA-ABC8-D9EA57CFDBBF}"/>
+    <workbookView xWindow="3132" yWindow="888" windowWidth="19908" windowHeight="12564" xr2:uid="{8DF5B536-FA94-48BA-ABC8-D9EA57CFDBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="GIP 2025" sheetId="1" r:id="rId1"/>
@@ -609,6 +609,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -621,22 +648,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -645,14 +660,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -732,15 +741,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -819,14 +819,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>40822</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>193222</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>176894</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1238250</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1390650</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>217716</xdr:rowOff>
     </xdr:to>
@@ -856,8 +856,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8327572" y="176894"/>
-          <a:ext cx="1197428" cy="1211036"/>
+          <a:off x="11489872" y="176894"/>
+          <a:ext cx="1197428" cy="1221922"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1278,149 +1278,149 @@
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="60"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="63"/>
     </row>
     <row r="2" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="90"/>
       <c r="B2" s="91"/>
       <c r="C2" s="92"/>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="66"/>
     </row>
     <row r="3" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="90"/>
       <c r="B3" s="91"/>
       <c r="C3" s="92"/>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="66"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="69"/>
     </row>
     <row r="4" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="90"/>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="58" t="s">
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="59"/>
-      <c r="V4" s="60"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="63"/>
     </row>
     <row r="5" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="90"/>
       <c r="B5" s="91"/>
       <c r="C5" s="92"/>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="63"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="66"/>
     </row>
     <row r="6" spans="1:35" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="93"/>
       <c r="B6" s="94"/>
       <c r="C6" s="95"/>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="86"/>
     </row>
     <row r="7" spans="1:35" ht="31.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="96" t="s">
@@ -1442,27 +1442,27 @@
       <c r="O7" s="97"/>
       <c r="P7" s="97"/>
       <c r="Q7" s="98"/>
-      <c r="R7" s="73" t="s">
+      <c r="R7" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="S7" s="74"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="74"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="74"/>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="74"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="53" t="s">
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="77"/>
+      <c r="Y7" s="77"/>
+      <c r="Z7" s="77"/>
+      <c r="AA7" s="77"/>
+      <c r="AB7" s="77"/>
+      <c r="AC7" s="77"/>
+      <c r="AD7" s="77"/>
+      <c r="AE7" s="78"/>
+      <c r="AF7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AG7" s="54"/>
-      <c r="AH7" s="54"/>
+      <c r="AG7" s="59"/>
+      <c r="AH7" s="59"/>
     </row>
     <row r="8" spans="1:35" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="99"/>
@@ -1482,109 +1482,109 @@
       <c r="O8" s="100"/>
       <c r="P8" s="100"/>
       <c r="Q8" s="101"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="77"/>
-      <c r="V8" s="77"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="77"/>
-      <c r="Y8" s="77"/>
-      <c r="Z8" s="77"/>
-      <c r="AA8" s="77"/>
-      <c r="AB8" s="77"/>
-      <c r="AC8" s="77"/>
-      <c r="AD8" s="77"/>
-      <c r="AE8" s="78"/>
-      <c r="AF8" s="55" t="s">
+      <c r="R8" s="79"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="80"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="80"/>
+      <c r="Z8" s="80"/>
+      <c r="AA8" s="80"/>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="80"/>
+      <c r="AD8" s="80"/>
+      <c r="AE8" s="81"/>
+      <c r="AF8" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="AG8" s="55" t="s">
+      <c r="AG8" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="AH8" s="55" t="s">
+      <c r="AH8" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AI8" s="55" t="s">
+      <c r="AI8" s="45" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A9" s="102"/>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="85" t="s">
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="54"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="55" t="s">
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="55" t="s">
+      <c r="L9" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="55" t="s">
+      <c r="M9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="55" t="s">
+      <c r="N9" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="85" t="s">
+      <c r="O9" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="55" t="s">
+      <c r="P9" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="55" t="s">
+      <c r="Q9" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="R9" s="43" t="s">
+      <c r="R9" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="S9" s="44"/>
-      <c r="T9" s="43" t="s">
+      <c r="S9" s="53"/>
+      <c r="T9" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="U9" s="44"/>
-      <c r="V9" s="43" t="s">
+      <c r="U9" s="53"/>
+      <c r="V9" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="W9" s="44"/>
-      <c r="X9" s="43" t="s">
+      <c r="W9" s="53"/>
+      <c r="X9" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="43" t="s">
+      <c r="Y9" s="53"/>
+      <c r="Z9" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="43" t="s">
+      <c r="AA9" s="53"/>
+      <c r="AB9" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="43" t="s">
+      <c r="AC9" s="53"/>
+      <c r="AD9" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="56"/>
-      <c r="AG9" s="56"/>
-      <c r="AH9" s="56"/>
-      <c r="AI9" s="56"/>
+      <c r="AE9" s="53"/>
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="46"/>
+      <c r="AI9" s="46"/>
     </row>
     <row r="10" spans="1:35" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A10" s="103"/>
-      <c r="B10" s="57"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="F10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="86"/>
+      <c r="G10" s="57"/>
       <c r="H10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1607,31 +1607,31 @@
       <c r="J10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="46"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="45"/>
-      <c r="AE10" s="46"/>
-      <c r="AF10" s="57"/>
-      <c r="AG10" s="57"/>
-      <c r="AH10" s="57"/>
-      <c r="AI10" s="57"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="55"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="55"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="55"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="55"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
     </row>
     <row r="11" spans="1:35" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
@@ -1663,8 +1663,8 @@
       <c r="AA11" s="42"/>
       <c r="AB11" s="41"/>
       <c r="AC11" s="42"/>
-      <c r="AD11" s="47"/>
-      <c r="AE11" s="48"/>
+      <c r="AD11" s="43"/>
+      <c r="AE11" s="44"/>
       <c r="AF11" s="20"/>
       <c r="AG11" s="20"/>
       <c r="AH11" s="20"/>
@@ -1700,8 +1700,8 @@
       <c r="AA12" s="42"/>
       <c r="AB12" s="41"/>
       <c r="AC12" s="42"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="48"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="44"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="20"/>
       <c r="AH12" s="20"/>
@@ -1733,12 +1733,12 @@
       <c r="W13" s="42"/>
       <c r="X13" s="41"/>
       <c r="Y13" s="42"/>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="47"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="48"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="44"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="43"/>
+      <c r="AE13" s="44"/>
       <c r="AF13" s="20"/>
       <c r="AG13" s="20"/>
       <c r="AH13" s="20"/>
@@ -1762,20 +1762,20 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="48"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="48"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="48"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="48"/>
-      <c r="AB14" s="47"/>
-      <c r="AC14" s="48"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="48"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="44"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="44"/>
+      <c r="Z14" s="43"/>
+      <c r="AA14" s="44"/>
+      <c r="AB14" s="43"/>
+      <c r="AC14" s="44"/>
+      <c r="AD14" s="43"/>
+      <c r="AE14" s="44"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="22"/>
       <c r="AH14" s="22"/>
@@ -1799,20 +1799,20 @@
       <c r="O15" s="5"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="3"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="52"/>
-      <c r="V15" s="51"/>
-      <c r="W15" s="52"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="49"/>
       <c r="X15" s="41"/>
       <c r="Y15" s="42"/>
       <c r="Z15" s="41"/>
       <c r="AA15" s="42"/>
       <c r="AB15" s="41"/>
       <c r="AC15" s="42"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="48"/>
+      <c r="AD15" s="43"/>
+      <c r="AE15" s="44"/>
       <c r="AF15" s="20"/>
       <c r="AG15" s="22"/>
       <c r="AH15" s="22"/>
@@ -1836,20 +1836,20 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="3"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="51"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="52"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="44"/>
       <c r="Z16" s="41"/>
       <c r="AA16" s="42"/>
       <c r="AB16" s="41"/>
       <c r="AC16" s="42"/>
-      <c r="AD16" s="47"/>
-      <c r="AE16" s="48"/>
+      <c r="AD16" s="43"/>
+      <c r="AE16" s="44"/>
       <c r="AF16" s="20"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="22"/>
@@ -1873,20 +1873,20 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="3"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="51"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="51"/>
-      <c r="W17" s="52"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="49"/>
       <c r="X17" s="41"/>
       <c r="Y17" s="42"/>
       <c r="Z17" s="41"/>
       <c r="AA17" s="42"/>
       <c r="AB17" s="41"/>
       <c r="AC17" s="42"/>
-      <c r="AD17" s="47"/>
-      <c r="AE17" s="48"/>
+      <c r="AD17" s="43"/>
+      <c r="AE17" s="44"/>
       <c r="AF17" s="20"/>
       <c r="AG17" s="1"/>
       <c r="AH17" s="22"/>
@@ -1910,20 +1910,20 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="52"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="52"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="49"/>
       <c r="X18" s="41"/>
       <c r="Y18" s="42"/>
       <c r="Z18" s="41"/>
       <c r="AA18" s="42"/>
       <c r="AB18" s="41"/>
       <c r="AC18" s="42"/>
-      <c r="AD18" s="47"/>
-      <c r="AE18" s="48"/>
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="44"/>
       <c r="AF18" s="20"/>
       <c r="AG18" s="20"/>
       <c r="AH18" s="20"/>
@@ -1947,20 +1947,20 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="47"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="47"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="47"/>
-      <c r="AE19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="51"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="44"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="44"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="44"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="44"/>
       <c r="AF19" s="22"/>
       <c r="AG19" s="1"/>
       <c r="AH19" s="22"/>
@@ -1984,20 +1984,20 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="3"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="52"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="52"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="49"/>
       <c r="X20" s="41"/>
       <c r="Y20" s="42"/>
       <c r="Z20" s="41"/>
       <c r="AA20" s="42"/>
       <c r="AB20" s="41"/>
       <c r="AC20" s="42"/>
-      <c r="AD20" s="47"/>
-      <c r="AE20" s="48"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="44"/>
       <c r="AF20" s="20"/>
       <c r="AG20" s="20"/>
       <c r="AH20" s="20"/>
@@ -2021,20 +2021,20 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="3"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="52"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="49"/>
       <c r="X21" s="41"/>
       <c r="Y21" s="42"/>
       <c r="Z21" s="41"/>
       <c r="AA21" s="42"/>
       <c r="AB21" s="41"/>
       <c r="AC21" s="42"/>
-      <c r="AD21" s="47"/>
-      <c r="AE21" s="48"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="44"/>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
       <c r="AH21" s="20"/>
@@ -2058,20 +2058,20 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="3"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="52"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="49"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="49"/>
       <c r="X22" s="41"/>
       <c r="Y22" s="42"/>
       <c r="Z22" s="41"/>
       <c r="AA22" s="42"/>
       <c r="AB22" s="41"/>
       <c r="AC22" s="42"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="48"/>
+      <c r="AD22" s="43"/>
+      <c r="AE22" s="44"/>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
       <c r="AH22" s="20"/>
@@ -2095,20 +2095,20 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="3"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="52"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="51"/>
-      <c r="W23" s="52"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="49"/>
       <c r="X23" s="41"/>
       <c r="Y23" s="42"/>
       <c r="Z23" s="41"/>
       <c r="AA23" s="42"/>
       <c r="AB23" s="41"/>
       <c r="AC23" s="42"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="48"/>
+      <c r="AD23" s="43"/>
+      <c r="AE23" s="44"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="20"/>
       <c r="AH23" s="20"/>
@@ -2132,20 +2132,20 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="3"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="52"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="52"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="52"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="49"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="49"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="49"/>
       <c r="X24" s="41"/>
       <c r="Y24" s="42"/>
       <c r="Z24" s="41"/>
       <c r="AA24" s="42"/>
       <c r="AB24" s="41"/>
       <c r="AC24" s="42"/>
-      <c r="AD24" s="47"/>
-      <c r="AE24" s="48"/>
+      <c r="AD24" s="43"/>
+      <c r="AE24" s="44"/>
       <c r="AF24" s="20"/>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
@@ -2169,20 +2169,20 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="3"/>
-      <c r="R25" s="51"/>
-      <c r="S25" s="52"/>
-      <c r="T25" s="51"/>
-      <c r="U25" s="52"/>
-      <c r="V25" s="51"/>
-      <c r="W25" s="52"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="49"/>
+      <c r="V25" s="48"/>
+      <c r="W25" s="49"/>
       <c r="X25" s="41"/>
       <c r="Y25" s="42"/>
       <c r="Z25" s="41"/>
       <c r="AA25" s="42"/>
       <c r="AB25" s="41"/>
       <c r="AC25" s="42"/>
-      <c r="AD25" s="47"/>
-      <c r="AE25" s="48"/>
+      <c r="AD25" s="43"/>
+      <c r="AE25" s="44"/>
       <c r="AF25" s="20"/>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
@@ -2206,20 +2206,20 @@
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="6"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="52"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="49"/>
       <c r="X26" s="41"/>
       <c r="Y26" s="42"/>
       <c r="Z26" s="41"/>
       <c r="AA26" s="42"/>
       <c r="AB26" s="41"/>
       <c r="AC26" s="42"/>
-      <c r="AD26" s="47"/>
-      <c r="AE26" s="48"/>
+      <c r="AD26" s="43"/>
+      <c r="AE26" s="44"/>
       <c r="AF26" s="20"/>
       <c r="AG26" s="22"/>
       <c r="AH26" s="22"/>
@@ -2243,20 +2243,20 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="52"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="49"/>
       <c r="X27" s="41"/>
       <c r="Y27" s="42"/>
       <c r="Z27" s="41"/>
       <c r="AA27" s="42"/>
       <c r="AB27" s="41"/>
       <c r="AC27" s="42"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="48"/>
+      <c r="AD27" s="43"/>
+      <c r="AE27" s="44"/>
       <c r="AF27" s="22"/>
       <c r="AG27" s="22"/>
       <c r="AH27" s="20"/>
@@ -2280,20 +2280,20 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="52"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="52"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="49"/>
       <c r="X28" s="41"/>
       <c r="Y28" s="42"/>
       <c r="Z28" s="41"/>
       <c r="AA28" s="42"/>
       <c r="AB28" s="41"/>
       <c r="AC28" s="42"/>
-      <c r="AD28" s="47"/>
-      <c r="AE28" s="48"/>
+      <c r="AD28" s="43"/>
+      <c r="AE28" s="44"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="22"/>
       <c r="AI28" s="21"/>
@@ -2316,20 +2316,20 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="52"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="49"/>
       <c r="X29" s="41"/>
       <c r="Y29" s="42"/>
       <c r="Z29" s="41"/>
       <c r="AA29" s="42"/>
       <c r="AB29" s="41"/>
       <c r="AC29" s="42"/>
-      <c r="AD29" s="47"/>
-      <c r="AE29" s="48"/>
+      <c r="AD29" s="43"/>
+      <c r="AE29" s="44"/>
       <c r="AF29" s="22"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="22"/>
@@ -2353,20 +2353,20 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="3"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="49"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="47"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="47"/>
-      <c r="AE30" s="48"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="50"/>
+      <c r="W30" s="51"/>
+      <c r="X30" s="43"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="43"/>
+      <c r="AA30" s="44"/>
+      <c r="AB30" s="43"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="43"/>
+      <c r="AE30" s="44"/>
       <c r="AF30" s="22"/>
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
@@ -2390,20 +2390,20 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="3"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="52"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="52"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="49"/>
       <c r="X31" s="41"/>
       <c r="Y31" s="42"/>
       <c r="Z31" s="41"/>
       <c r="AA31" s="42"/>
       <c r="AB31" s="41"/>
       <c r="AC31" s="42"/>
-      <c r="AD31" s="47"/>
-      <c r="AE31" s="48"/>
+      <c r="AD31" s="43"/>
+      <c r="AE31" s="44"/>
       <c r="AF31" s="20"/>
       <c r="AG31" s="22"/>
       <c r="AH31" s="22"/>
@@ -2427,20 +2427,20 @@
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="51"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="51"/>
-      <c r="W32" s="52"/>
+      <c r="R32" s="48"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="48"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="48"/>
+      <c r="W32" s="49"/>
       <c r="X32" s="41"/>
       <c r="Y32" s="42"/>
       <c r="Z32" s="41"/>
       <c r="AA32" s="42"/>
       <c r="AB32" s="41"/>
       <c r="AC32" s="42"/>
-      <c r="AD32" s="47"/>
-      <c r="AE32" s="48"/>
+      <c r="AD32" s="43"/>
+      <c r="AE32" s="44"/>
       <c r="AF32" s="22"/>
       <c r="AG32" s="22"/>
       <c r="AH32" s="22"/>
@@ -2464,20 +2464,20 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="3"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="52"/>
-      <c r="T33" s="51"/>
-      <c r="U33" s="52"/>
-      <c r="V33" s="51"/>
-      <c r="W33" s="52"/>
+      <c r="R33" s="48"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="48"/>
+      <c r="W33" s="49"/>
       <c r="X33" s="41"/>
       <c r="Y33" s="42"/>
       <c r="Z33" s="41"/>
       <c r="AA33" s="42"/>
       <c r="AB33" s="41"/>
       <c r="AC33" s="42"/>
-      <c r="AD33" s="47"/>
-      <c r="AE33" s="48"/>
+      <c r="AD33" s="43"/>
+      <c r="AE33" s="44"/>
       <c r="AF33" s="22"/>
       <c r="AG33" s="1"/>
       <c r="AH33" s="22"/>
@@ -2501,20 +2501,20 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="51"/>
-      <c r="S34" s="52"/>
-      <c r="T34" s="51"/>
-      <c r="U34" s="52"/>
-      <c r="V34" s="51"/>
-      <c r="W34" s="52"/>
+      <c r="R34" s="48"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="48"/>
+      <c r="W34" s="49"/>
       <c r="X34" s="41"/>
       <c r="Y34" s="42"/>
       <c r="Z34" s="41"/>
       <c r="AA34" s="42"/>
       <c r="AB34" s="41"/>
       <c r="AC34" s="42"/>
-      <c r="AD34" s="47"/>
-      <c r="AE34" s="48"/>
+      <c r="AD34" s="43"/>
+      <c r="AE34" s="44"/>
       <c r="AF34" s="22"/>
       <c r="AG34" s="1"/>
       <c r="AH34" s="22"/>
@@ -2538,20 +2538,20 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="3"/>
-      <c r="R35" s="49"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="49"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="48"/>
-      <c r="AB35" s="47"/>
-      <c r="AC35" s="48"/>
-      <c r="AD35" s="47"/>
-      <c r="AE35" s="48"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="51"/>
+      <c r="V35" s="50"/>
+      <c r="W35" s="51"/>
+      <c r="X35" s="43"/>
+      <c r="Y35" s="44"/>
+      <c r="Z35" s="43"/>
+      <c r="AA35" s="44"/>
+      <c r="AB35" s="43"/>
+      <c r="AC35" s="44"/>
+      <c r="AD35" s="43"/>
+      <c r="AE35" s="44"/>
       <c r="AF35" s="22"/>
       <c r="AG35" s="22"/>
       <c r="AH35" s="22"/>
@@ -2575,20 +2575,20 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="3"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="52"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="48"/>
+      <c r="W36" s="49"/>
       <c r="X36" s="41"/>
       <c r="Y36" s="42"/>
       <c r="Z36" s="41"/>
       <c r="AA36" s="42"/>
       <c r="AB36" s="41"/>
       <c r="AC36" s="42"/>
-      <c r="AD36" s="47"/>
-      <c r="AE36" s="48"/>
+      <c r="AD36" s="43"/>
+      <c r="AE36" s="44"/>
       <c r="AF36" s="22"/>
       <c r="AG36" s="1"/>
       <c r="AI36" s="21"/>
@@ -2611,20 +2611,20 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="3"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="52"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="52"/>
+      <c r="R37" s="48"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="48"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="48"/>
+      <c r="W37" s="49"/>
       <c r="X37" s="41"/>
       <c r="Y37" s="42"/>
       <c r="Z37" s="41"/>
       <c r="AA37" s="42"/>
       <c r="AB37" s="41"/>
       <c r="AC37" s="42"/>
-      <c r="AD37" s="47"/>
-      <c r="AE37" s="48"/>
+      <c r="AD37" s="43"/>
+      <c r="AE37" s="44"/>
       <c r="AF37" s="22"/>
       <c r="AG37" s="22"/>
       <c r="AH37" s="22"/>
@@ -2648,20 +2648,20 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="3"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="52"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="52"/>
+      <c r="R38" s="48"/>
+      <c r="S38" s="49"/>
+      <c r="T38" s="48"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="48"/>
+      <c r="W38" s="49"/>
       <c r="X38" s="41"/>
       <c r="Y38" s="42"/>
       <c r="Z38" s="41"/>
       <c r="AA38" s="42"/>
       <c r="AB38" s="41"/>
       <c r="AC38" s="42"/>
-      <c r="AD38" s="47"/>
-      <c r="AE38" s="48"/>
+      <c r="AD38" s="43"/>
+      <c r="AE38" s="44"/>
       <c r="AF38" s="22"/>
       <c r="AG38" s="1"/>
       <c r="AH38" s="22"/>
@@ -2685,20 +2685,20 @@
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="3"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="52"/>
-      <c r="V39" s="51"/>
-      <c r="W39" s="52"/>
+      <c r="R39" s="48"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="48"/>
+      <c r="W39" s="49"/>
       <c r="X39" s="41"/>
       <c r="Y39" s="42"/>
       <c r="Z39" s="41"/>
       <c r="AA39" s="42"/>
       <c r="AB39" s="41"/>
       <c r="AC39" s="42"/>
-      <c r="AD39" s="47"/>
-      <c r="AE39" s="48"/>
+      <c r="AD39" s="43"/>
+      <c r="AE39" s="44"/>
       <c r="AF39" s="22"/>
       <c r="AG39" s="1"/>
       <c r="AH39" s="22"/>
@@ -2722,20 +2722,20 @@
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="3"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="52"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="52"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="49"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="48"/>
+      <c r="W40" s="49"/>
       <c r="X40" s="41"/>
       <c r="Y40" s="42"/>
       <c r="Z40" s="41"/>
       <c r="AA40" s="42"/>
       <c r="AB40" s="41"/>
       <c r="AC40" s="42"/>
-      <c r="AD40" s="47"/>
-      <c r="AE40" s="48"/>
+      <c r="AD40" s="43"/>
+      <c r="AE40" s="44"/>
       <c r="AF40" s="22"/>
       <c r="AG40" s="22"/>
       <c r="AH40" s="22"/>
@@ -2759,20 +2759,20 @@
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="3"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="52"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="52"/>
-      <c r="V41" s="51"/>
-      <c r="W41" s="52"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="48"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="48"/>
+      <c r="W41" s="49"/>
       <c r="X41" s="41"/>
       <c r="Y41" s="42"/>
       <c r="Z41" s="41"/>
       <c r="AA41" s="42"/>
       <c r="AB41" s="41"/>
       <c r="AC41" s="42"/>
-      <c r="AD41" s="47"/>
-      <c r="AE41" s="48"/>
+      <c r="AD41" s="43"/>
+      <c r="AE41" s="44"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="22"/>
       <c r="AH41" s="22"/>
@@ -2796,20 +2796,20 @@
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
       <c r="Q42" s="3"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="52"/>
-      <c r="T42" s="51"/>
-      <c r="U42" s="52"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="52"/>
+      <c r="R42" s="48"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="48"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="48"/>
+      <c r="W42" s="49"/>
       <c r="X42" s="41"/>
       <c r="Y42" s="42"/>
       <c r="Z42" s="41"/>
       <c r="AA42" s="42"/>
       <c r="AB42" s="41"/>
       <c r="AC42" s="42"/>
-      <c r="AD42" s="47"/>
-      <c r="AE42" s="48"/>
+      <c r="AD42" s="43"/>
+      <c r="AE42" s="44"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="22"/>
       <c r="AH42" s="22"/>
@@ -2833,20 +2833,20 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="3"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="52"/>
-      <c r="T43" s="51"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="51"/>
-      <c r="W43" s="52"/>
+      <c r="R43" s="48"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="48"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="48"/>
+      <c r="W43" s="49"/>
       <c r="X43" s="41"/>
       <c r="Y43" s="42"/>
       <c r="Z43" s="41"/>
       <c r="AA43" s="42"/>
       <c r="AB43" s="41"/>
       <c r="AC43" s="42"/>
-      <c r="AD43" s="47"/>
-      <c r="AE43" s="48"/>
+      <c r="AD43" s="43"/>
+      <c r="AE43" s="44"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
@@ -2870,20 +2870,20 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
       <c r="Q44" s="3"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="51"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="51"/>
-      <c r="W44" s="52"/>
+      <c r="R44" s="48"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="48"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="48"/>
+      <c r="W44" s="49"/>
       <c r="X44" s="41"/>
       <c r="Y44" s="42"/>
       <c r="Z44" s="41"/>
       <c r="AA44" s="42"/>
       <c r="AB44" s="41"/>
       <c r="AC44" s="42"/>
-      <c r="AD44" s="47"/>
-      <c r="AE44" s="48"/>
+      <c r="AD44" s="43"/>
+      <c r="AE44" s="44"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
@@ -2907,20 +2907,20 @@
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
       <c r="Q45" s="3"/>
-      <c r="R45" s="49"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="49"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="49"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="48"/>
-      <c r="AB45" s="47"/>
-      <c r="AC45" s="48"/>
-      <c r="AD45" s="47"/>
-      <c r="AE45" s="48"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="51"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="51"/>
+      <c r="V45" s="50"/>
+      <c r="W45" s="51"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="43"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="44"/>
+      <c r="AD45" s="43"/>
+      <c r="AE45" s="44"/>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
@@ -2944,20 +2944,20 @@
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
       <c r="Q46" s="3"/>
-      <c r="R46" s="51"/>
-      <c r="S46" s="52"/>
-      <c r="T46" s="51"/>
-      <c r="U46" s="52"/>
-      <c r="V46" s="51"/>
-      <c r="W46" s="52"/>
+      <c r="R46" s="48"/>
+      <c r="S46" s="49"/>
+      <c r="T46" s="48"/>
+      <c r="U46" s="49"/>
+      <c r="V46" s="48"/>
+      <c r="W46" s="49"/>
       <c r="X46" s="41"/>
       <c r="Y46" s="42"/>
       <c r="Z46" s="41"/>
       <c r="AA46" s="42"/>
       <c r="AB46" s="41"/>
       <c r="AC46" s="42"/>
-      <c r="AD46" s="47"/>
-      <c r="AE46" s="48"/>
+      <c r="AD46" s="43"/>
+      <c r="AE46" s="44"/>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
@@ -2981,20 +2981,20 @@
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
       <c r="Q47" s="3"/>
-      <c r="R47" s="51"/>
-      <c r="S47" s="52"/>
-      <c r="T47" s="51"/>
-      <c r="U47" s="52"/>
-      <c r="V47" s="51"/>
-      <c r="W47" s="52"/>
+      <c r="R47" s="48"/>
+      <c r="S47" s="49"/>
+      <c r="T47" s="48"/>
+      <c r="U47" s="49"/>
+      <c r="V47" s="48"/>
+      <c r="W47" s="49"/>
       <c r="X47" s="41"/>
       <c r="Y47" s="42"/>
       <c r="Z47" s="41"/>
       <c r="AA47" s="42"/>
       <c r="AB47" s="41"/>
       <c r="AC47" s="42"/>
-      <c r="AD47" s="47"/>
-      <c r="AE47" s="48"/>
+      <c r="AD47" s="43"/>
+      <c r="AE47" s="44"/>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
@@ -3018,20 +3018,20 @@
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
       <c r="Q48" s="3"/>
-      <c r="R48" s="51"/>
-      <c r="S48" s="52"/>
-      <c r="T48" s="51"/>
-      <c r="U48" s="52"/>
-      <c r="V48" s="51"/>
-      <c r="W48" s="52"/>
+      <c r="R48" s="48"/>
+      <c r="S48" s="49"/>
+      <c r="T48" s="48"/>
+      <c r="U48" s="49"/>
+      <c r="V48" s="48"/>
+      <c r="W48" s="49"/>
       <c r="X48" s="41"/>
       <c r="Y48" s="42"/>
       <c r="Z48" s="41"/>
       <c r="AA48" s="42"/>
       <c r="AB48" s="41"/>
       <c r="AC48" s="42"/>
-      <c r="AD48" s="47"/>
-      <c r="AE48" s="48"/>
+      <c r="AD48" s="43"/>
+      <c r="AE48" s="44"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
@@ -3055,20 +3055,20 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="3"/>
-      <c r="R49" s="51"/>
-      <c r="S49" s="52"/>
-      <c r="T49" s="51"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="51"/>
-      <c r="W49" s="52"/>
+      <c r="R49" s="48"/>
+      <c r="S49" s="49"/>
+      <c r="T49" s="48"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="48"/>
+      <c r="W49" s="49"/>
       <c r="X49" s="41"/>
       <c r="Y49" s="42"/>
       <c r="Z49" s="41"/>
       <c r="AA49" s="42"/>
       <c r="AB49" s="41"/>
       <c r="AC49" s="42"/>
-      <c r="AD49" s="47"/>
-      <c r="AE49" s="48"/>
+      <c r="AD49" s="43"/>
+      <c r="AE49" s="44"/>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
@@ -3092,20 +3092,20 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="3"/>
-      <c r="R50" s="51"/>
-      <c r="S50" s="52"/>
-      <c r="T50" s="51"/>
-      <c r="U50" s="52"/>
-      <c r="V50" s="51"/>
-      <c r="W50" s="52"/>
+      <c r="R50" s="48"/>
+      <c r="S50" s="49"/>
+      <c r="T50" s="48"/>
+      <c r="U50" s="49"/>
+      <c r="V50" s="48"/>
+      <c r="W50" s="49"/>
       <c r="X50" s="41"/>
       <c r="Y50" s="42"/>
       <c r="Z50" s="41"/>
       <c r="AA50" s="42"/>
       <c r="AB50" s="41"/>
       <c r="AC50" s="42"/>
-      <c r="AD50" s="47"/>
-      <c r="AE50" s="48"/>
+      <c r="AD50" s="43"/>
+      <c r="AE50" s="44"/>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
@@ -3129,20 +3129,20 @@
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="3"/>
-      <c r="R51" s="51"/>
-      <c r="S51" s="52"/>
-      <c r="T51" s="51"/>
-      <c r="U51" s="52"/>
-      <c r="V51" s="51"/>
-      <c r="W51" s="52"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="49"/>
+      <c r="T51" s="48"/>
+      <c r="U51" s="49"/>
+      <c r="V51" s="48"/>
+      <c r="W51" s="49"/>
       <c r="X51" s="41"/>
       <c r="Y51" s="42"/>
       <c r="Z51" s="41"/>
       <c r="AA51" s="42"/>
       <c r="AB51" s="41"/>
       <c r="AC51" s="42"/>
-      <c r="AD51" s="47"/>
-      <c r="AE51" s="48"/>
+      <c r="AD51" s="43"/>
+      <c r="AE51" s="44"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
@@ -3166,20 +3166,20 @@
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="3"/>
-      <c r="R52" s="51"/>
-      <c r="S52" s="52"/>
-      <c r="T52" s="51"/>
-      <c r="U52" s="52"/>
-      <c r="V52" s="51"/>
-      <c r="W52" s="52"/>
+      <c r="R52" s="48"/>
+      <c r="S52" s="49"/>
+      <c r="T52" s="48"/>
+      <c r="U52" s="49"/>
+      <c r="V52" s="48"/>
+      <c r="W52" s="49"/>
       <c r="X52" s="41"/>
       <c r="Y52" s="42"/>
       <c r="Z52" s="41"/>
       <c r="AA52" s="42"/>
       <c r="AB52" s="41"/>
       <c r="AC52" s="42"/>
-      <c r="AD52" s="47"/>
-      <c r="AE52" s="48"/>
+      <c r="AD52" s="43"/>
+      <c r="AE52" s="44"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
@@ -3203,20 +3203,20 @@
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
       <c r="Q53" s="3"/>
-      <c r="R53" s="51"/>
-      <c r="S53" s="52"/>
-      <c r="T53" s="51"/>
-      <c r="U53" s="52"/>
-      <c r="V53" s="51"/>
-      <c r="W53" s="52"/>
+      <c r="R53" s="48"/>
+      <c r="S53" s="49"/>
+      <c r="T53" s="48"/>
+      <c r="U53" s="49"/>
+      <c r="V53" s="48"/>
+      <c r="W53" s="49"/>
       <c r="X53" s="41"/>
       <c r="Y53" s="42"/>
       <c r="Z53" s="41"/>
       <c r="AA53" s="42"/>
       <c r="AB53" s="41"/>
       <c r="AC53" s="42"/>
-      <c r="AD53" s="47"/>
-      <c r="AE53" s="48"/>
+      <c r="AD53" s="43"/>
+      <c r="AE53" s="44"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
@@ -3240,20 +3240,20 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
       <c r="Q54" s="3"/>
-      <c r="R54" s="51"/>
-      <c r="S54" s="52"/>
-      <c r="T54" s="51"/>
-      <c r="U54" s="52"/>
-      <c r="V54" s="51"/>
-      <c r="W54" s="52"/>
+      <c r="R54" s="48"/>
+      <c r="S54" s="49"/>
+      <c r="T54" s="48"/>
+      <c r="U54" s="49"/>
+      <c r="V54" s="48"/>
+      <c r="W54" s="49"/>
       <c r="X54" s="41"/>
       <c r="Y54" s="42"/>
       <c r="Z54" s="41"/>
       <c r="AA54" s="42"/>
       <c r="AB54" s="41"/>
       <c r="AC54" s="42"/>
-      <c r="AD54" s="47"/>
-      <c r="AE54" s="48"/>
+      <c r="AD54" s="43"/>
+      <c r="AE54" s="44"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
@@ -3277,20 +3277,20 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
       <c r="Q55" s="3"/>
-      <c r="R55" s="51"/>
-      <c r="S55" s="52"/>
-      <c r="T55" s="51"/>
-      <c r="U55" s="52"/>
-      <c r="V55" s="51"/>
-      <c r="W55" s="52"/>
+      <c r="R55" s="48"/>
+      <c r="S55" s="49"/>
+      <c r="T55" s="48"/>
+      <c r="U55" s="49"/>
+      <c r="V55" s="48"/>
+      <c r="W55" s="49"/>
       <c r="X55" s="41"/>
       <c r="Y55" s="42"/>
       <c r="Z55" s="41"/>
       <c r="AA55" s="42"/>
       <c r="AB55" s="41"/>
       <c r="AC55" s="42"/>
-      <c r="AD55" s="47"/>
-      <c r="AE55" s="48"/>
+      <c r="AD55" s="43"/>
+      <c r="AE55" s="44"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
@@ -3314,20 +3314,20 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="3"/>
-      <c r="R56" s="51"/>
-      <c r="S56" s="52"/>
-      <c r="T56" s="51"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="51"/>
-      <c r="W56" s="52"/>
+      <c r="R56" s="48"/>
+      <c r="S56" s="49"/>
+      <c r="T56" s="48"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="48"/>
+      <c r="W56" s="49"/>
       <c r="X56" s="41"/>
       <c r="Y56" s="42"/>
       <c r="Z56" s="41"/>
       <c r="AA56" s="42"/>
       <c r="AB56" s="41"/>
       <c r="AC56" s="42"/>
-      <c r="AD56" s="47"/>
-      <c r="AE56" s="48"/>
+      <c r="AD56" s="43"/>
+      <c r="AE56" s="44"/>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
@@ -3351,20 +3351,20 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
       <c r="Q57" s="3"/>
-      <c r="R57" s="51"/>
-      <c r="S57" s="52"/>
-      <c r="T57" s="51"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="51"/>
-      <c r="W57" s="52"/>
+      <c r="R57" s="48"/>
+      <c r="S57" s="49"/>
+      <c r="T57" s="48"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="48"/>
+      <c r="W57" s="49"/>
       <c r="X57" s="41"/>
       <c r="Y57" s="42"/>
       <c r="Z57" s="41"/>
       <c r="AA57" s="42"/>
       <c r="AB57" s="41"/>
       <c r="AC57" s="42"/>
-      <c r="AD57" s="47"/>
-      <c r="AE57" s="48"/>
+      <c r="AD57" s="43"/>
+      <c r="AE57" s="44"/>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
@@ -3388,20 +3388,20 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
       <c r="Q58" s="3"/>
-      <c r="R58" s="51"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="51"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="51"/>
-      <c r="W58" s="52"/>
+      <c r="R58" s="48"/>
+      <c r="S58" s="49"/>
+      <c r="T58" s="48"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="48"/>
+      <c r="W58" s="49"/>
       <c r="X58" s="41"/>
       <c r="Y58" s="42"/>
       <c r="Z58" s="41"/>
       <c r="AA58" s="42"/>
       <c r="AB58" s="41"/>
       <c r="AC58" s="42"/>
-      <c r="AD58" s="47"/>
-      <c r="AE58" s="48"/>
+      <c r="AD58" s="43"/>
+      <c r="AE58" s="44"/>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
@@ -3425,20 +3425,20 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
       <c r="Q59" s="3"/>
-      <c r="R59" s="51"/>
-      <c r="S59" s="52"/>
-      <c r="T59" s="51"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="51"/>
-      <c r="W59" s="52"/>
+      <c r="R59" s="48"/>
+      <c r="S59" s="49"/>
+      <c r="T59" s="48"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="48"/>
+      <c r="W59" s="49"/>
       <c r="X59" s="41"/>
       <c r="Y59" s="42"/>
       <c r="Z59" s="41"/>
       <c r="AA59" s="42"/>
       <c r="AB59" s="41"/>
       <c r="AC59" s="42"/>
-      <c r="AD59" s="47"/>
-      <c r="AE59" s="48"/>
+      <c r="AD59" s="43"/>
+      <c r="AE59" s="44"/>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
@@ -3462,20 +3462,20 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
       <c r="Q60" s="3"/>
-      <c r="R60" s="51"/>
-      <c r="S60" s="52"/>
-      <c r="T60" s="51"/>
-      <c r="U60" s="52"/>
-      <c r="V60" s="51"/>
-      <c r="W60" s="52"/>
+      <c r="R60" s="48"/>
+      <c r="S60" s="49"/>
+      <c r="T60" s="48"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="48"/>
+      <c r="W60" s="49"/>
       <c r="X60" s="41"/>
       <c r="Y60" s="42"/>
       <c r="Z60" s="41"/>
       <c r="AA60" s="42"/>
       <c r="AB60" s="41"/>
       <c r="AC60" s="42"/>
-      <c r="AD60" s="47"/>
-      <c r="AE60" s="48"/>
+      <c r="AD60" s="43"/>
+      <c r="AE60" s="44"/>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
@@ -3499,20 +3499,20 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
       <c r="Q61" s="3"/>
-      <c r="R61" s="51"/>
-      <c r="S61" s="52"/>
-      <c r="T61" s="51"/>
-      <c r="U61" s="52"/>
-      <c r="V61" s="51"/>
-      <c r="W61" s="52"/>
+      <c r="R61" s="48"/>
+      <c r="S61" s="49"/>
+      <c r="T61" s="48"/>
+      <c r="U61" s="49"/>
+      <c r="V61" s="48"/>
+      <c r="W61" s="49"/>
       <c r="X61" s="41"/>
       <c r="Y61" s="42"/>
       <c r="Z61" s="41"/>
       <c r="AA61" s="42"/>
       <c r="AB61" s="41"/>
       <c r="AC61" s="42"/>
-      <c r="AD61" s="47"/>
-      <c r="AE61" s="48"/>
+      <c r="AD61" s="43"/>
+      <c r="AE61" s="44"/>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
@@ -3535,20 +3535,20 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
       <c r="Q62" s="3"/>
-      <c r="R62" s="51"/>
-      <c r="S62" s="52"/>
-      <c r="T62" s="51"/>
-      <c r="U62" s="52"/>
-      <c r="V62" s="51"/>
-      <c r="W62" s="52"/>
+      <c r="R62" s="48"/>
+      <c r="S62" s="49"/>
+      <c r="T62" s="48"/>
+      <c r="U62" s="49"/>
+      <c r="V62" s="48"/>
+      <c r="W62" s="49"/>
       <c r="X62" s="41"/>
       <c r="Y62" s="42"/>
       <c r="Z62" s="41"/>
       <c r="AA62" s="42"/>
       <c r="AB62" s="41"/>
       <c r="AC62" s="42"/>
-      <c r="AD62" s="47"/>
-      <c r="AE62" s="48"/>
+      <c r="AD62" s="43"/>
+      <c r="AE62" s="44"/>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
@@ -3572,20 +3572,20 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
       <c r="Q63" s="3"/>
-      <c r="R63" s="51"/>
-      <c r="S63" s="52"/>
-      <c r="T63" s="51"/>
-      <c r="U63" s="52"/>
-      <c r="V63" s="51"/>
-      <c r="W63" s="52"/>
+      <c r="R63" s="48"/>
+      <c r="S63" s="49"/>
+      <c r="T63" s="48"/>
+      <c r="U63" s="49"/>
+      <c r="V63" s="48"/>
+      <c r="W63" s="49"/>
       <c r="X63" s="41"/>
       <c r="Y63" s="42"/>
       <c r="Z63" s="41"/>
       <c r="AA63" s="42"/>
       <c r="AB63" s="41"/>
       <c r="AC63" s="42"/>
-      <c r="AD63" s="47"/>
-      <c r="AE63" s="48"/>
+      <c r="AD63" s="43"/>
+      <c r="AE63" s="44"/>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
@@ -3609,20 +3609,20 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
       <c r="Q64" s="3"/>
-      <c r="R64" s="51"/>
-      <c r="S64" s="52"/>
-      <c r="T64" s="51"/>
-      <c r="U64" s="52"/>
-      <c r="V64" s="51"/>
-      <c r="W64" s="52"/>
+      <c r="R64" s="48"/>
+      <c r="S64" s="49"/>
+      <c r="T64" s="48"/>
+      <c r="U64" s="49"/>
+      <c r="V64" s="48"/>
+      <c r="W64" s="49"/>
       <c r="X64" s="41"/>
       <c r="Y64" s="42"/>
       <c r="Z64" s="41"/>
       <c r="AA64" s="42"/>
       <c r="AB64" s="41"/>
       <c r="AC64" s="42"/>
-      <c r="AD64" s="47"/>
-      <c r="AE64" s="48"/>
+      <c r="AD64" s="43"/>
+      <c r="AE64" s="44"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
@@ -3646,20 +3646,20 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
       <c r="Q65" s="3"/>
-      <c r="R65" s="51"/>
-      <c r="S65" s="52"/>
-      <c r="T65" s="51"/>
-      <c r="U65" s="52"/>
-      <c r="V65" s="51"/>
-      <c r="W65" s="52"/>
+      <c r="R65" s="48"/>
+      <c r="S65" s="49"/>
+      <c r="T65" s="48"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="48"/>
+      <c r="W65" s="49"/>
       <c r="X65" s="41"/>
       <c r="Y65" s="42"/>
       <c r="Z65" s="41"/>
       <c r="AA65" s="42"/>
       <c r="AB65" s="41"/>
       <c r="AC65" s="42"/>
-      <c r="AD65" s="47"/>
-      <c r="AE65" s="48"/>
+      <c r="AD65" s="43"/>
+      <c r="AE65" s="44"/>
       <c r="AF65" s="22"/>
       <c r="AG65" s="22"/>
       <c r="AH65" s="22"/>
@@ -3683,20 +3683,20 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
       <c r="Q66" s="3"/>
-      <c r="R66" s="51"/>
-      <c r="S66" s="52"/>
-      <c r="T66" s="51"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="51"/>
-      <c r="W66" s="52"/>
+      <c r="R66" s="48"/>
+      <c r="S66" s="49"/>
+      <c r="T66" s="48"/>
+      <c r="U66" s="49"/>
+      <c r="V66" s="48"/>
+      <c r="W66" s="49"/>
       <c r="X66" s="41"/>
       <c r="Y66" s="42"/>
       <c r="Z66" s="41"/>
       <c r="AA66" s="42"/>
       <c r="AB66" s="41"/>
       <c r="AC66" s="42"/>
-      <c r="AD66" s="47"/>
-      <c r="AE66" s="48"/>
+      <c r="AD66" s="43"/>
+      <c r="AE66" s="44"/>
       <c r="AF66" s="22"/>
       <c r="AG66" s="22"/>
       <c r="AH66" s="22"/>
@@ -3720,20 +3720,20 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="3"/>
-      <c r="R67" s="51"/>
-      <c r="S67" s="52"/>
-      <c r="T67" s="51"/>
-      <c r="U67" s="52"/>
-      <c r="V67" s="51"/>
-      <c r="W67" s="52"/>
+      <c r="R67" s="48"/>
+      <c r="S67" s="49"/>
+      <c r="T67" s="48"/>
+      <c r="U67" s="49"/>
+      <c r="V67" s="48"/>
+      <c r="W67" s="49"/>
       <c r="X67" s="41"/>
       <c r="Y67" s="42"/>
       <c r="Z67" s="41"/>
       <c r="AA67" s="42"/>
       <c r="AB67" s="41"/>
       <c r="AC67" s="42"/>
-      <c r="AD67" s="47"/>
-      <c r="AE67" s="48"/>
+      <c r="AD67" s="43"/>
+      <c r="AE67" s="44"/>
       <c r="AF67" s="22"/>
       <c r="AG67" s="22"/>
       <c r="AH67" s="22"/>
@@ -3757,20 +3757,20 @@
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
       <c r="Q68" s="3"/>
-      <c r="R68" s="51"/>
-      <c r="S68" s="52"/>
-      <c r="T68" s="51"/>
-      <c r="U68" s="52"/>
-      <c r="V68" s="51"/>
-      <c r="W68" s="52"/>
+      <c r="R68" s="48"/>
+      <c r="S68" s="49"/>
+      <c r="T68" s="48"/>
+      <c r="U68" s="49"/>
+      <c r="V68" s="48"/>
+      <c r="W68" s="49"/>
       <c r="X68" s="41"/>
       <c r="Y68" s="42"/>
       <c r="Z68" s="41"/>
       <c r="AA68" s="42"/>
       <c r="AB68" s="41"/>
       <c r="AC68" s="42"/>
-      <c r="AD68" s="47"/>
-      <c r="AE68" s="48"/>
+      <c r="AD68" s="43"/>
+      <c r="AE68" s="44"/>
       <c r="AF68" s="22"/>
       <c r="AG68" s="22"/>
       <c r="AH68" s="22"/>
@@ -3794,20 +3794,20 @@
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
       <c r="Q69" s="3"/>
-      <c r="R69" s="51"/>
-      <c r="S69" s="52"/>
-      <c r="T69" s="51"/>
-      <c r="U69" s="52"/>
-      <c r="V69" s="51"/>
-      <c r="W69" s="52"/>
+      <c r="R69" s="48"/>
+      <c r="S69" s="49"/>
+      <c r="T69" s="48"/>
+      <c r="U69" s="49"/>
+      <c r="V69" s="48"/>
+      <c r="W69" s="49"/>
       <c r="X69" s="41"/>
       <c r="Y69" s="42"/>
       <c r="Z69" s="41"/>
       <c r="AA69" s="42"/>
       <c r="AB69" s="41"/>
       <c r="AC69" s="42"/>
-      <c r="AD69" s="47"/>
-      <c r="AE69" s="48"/>
+      <c r="AD69" s="43"/>
+      <c r="AE69" s="44"/>
       <c r="AF69" s="22"/>
       <c r="AG69" s="22"/>
       <c r="AH69" s="22"/>
@@ -3831,20 +3831,20 @@
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
       <c r="Q70" s="3"/>
-      <c r="R70" s="51"/>
-      <c r="S70" s="52"/>
-      <c r="T70" s="51"/>
-      <c r="U70" s="52"/>
-      <c r="V70" s="51"/>
-      <c r="W70" s="52"/>
+      <c r="R70" s="48"/>
+      <c r="S70" s="49"/>
+      <c r="T70" s="48"/>
+      <c r="U70" s="49"/>
+      <c r="V70" s="48"/>
+      <c r="W70" s="49"/>
       <c r="X70" s="41"/>
       <c r="Y70" s="42"/>
       <c r="Z70" s="41"/>
       <c r="AA70" s="42"/>
       <c r="AB70" s="41"/>
       <c r="AC70" s="42"/>
-      <c r="AD70" s="47"/>
-      <c r="AE70" s="48"/>
+      <c r="AD70" s="43"/>
+      <c r="AE70" s="44"/>
       <c r="AF70" s="22"/>
       <c r="AG70" s="22"/>
       <c r="AH70" s="22"/>
@@ -3868,20 +3868,20 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
       <c r="Q71" s="3"/>
-      <c r="R71" s="51"/>
-      <c r="S71" s="52"/>
-      <c r="T71" s="51"/>
-      <c r="U71" s="52"/>
-      <c r="V71" s="51"/>
-      <c r="W71" s="52"/>
+      <c r="R71" s="48"/>
+      <c r="S71" s="49"/>
+      <c r="T71" s="48"/>
+      <c r="U71" s="49"/>
+      <c r="V71" s="48"/>
+      <c r="W71" s="49"/>
       <c r="X71" s="41"/>
       <c r="Y71" s="42"/>
       <c r="Z71" s="41"/>
       <c r="AA71" s="42"/>
       <c r="AB71" s="41"/>
       <c r="AC71" s="42"/>
-      <c r="AD71" s="47"/>
-      <c r="AE71" s="48"/>
+      <c r="AD71" s="43"/>
+      <c r="AE71" s="44"/>
       <c r="AF71" s="22"/>
       <c r="AG71" s="22"/>
       <c r="AH71" s="22"/>
@@ -3905,20 +3905,20 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="3"/>
-      <c r="R72" s="51"/>
-      <c r="S72" s="52"/>
-      <c r="T72" s="51"/>
-      <c r="U72" s="52"/>
-      <c r="V72" s="51"/>
-      <c r="W72" s="52"/>
+      <c r="R72" s="48"/>
+      <c r="S72" s="49"/>
+      <c r="T72" s="48"/>
+      <c r="U72" s="49"/>
+      <c r="V72" s="48"/>
+      <c r="W72" s="49"/>
       <c r="X72" s="41"/>
       <c r="Y72" s="42"/>
       <c r="Z72" s="41"/>
       <c r="AA72" s="42"/>
       <c r="AB72" s="41"/>
       <c r="AC72" s="42"/>
-      <c r="AD72" s="47"/>
-      <c r="AE72" s="48"/>
+      <c r="AD72" s="43"/>
+      <c r="AE72" s="44"/>
       <c r="AF72" s="22"/>
       <c r="AG72" s="22"/>
       <c r="AH72" s="22"/>
@@ -3942,20 +3942,20 @@
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
       <c r="Q73" s="3"/>
-      <c r="R73" s="51"/>
-      <c r="S73" s="52"/>
-      <c r="T73" s="51"/>
-      <c r="U73" s="52"/>
-      <c r="V73" s="51"/>
-      <c r="W73" s="52"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="49"/>
+      <c r="T73" s="48"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="48"/>
+      <c r="W73" s="49"/>
       <c r="X73" s="41"/>
       <c r="Y73" s="42"/>
       <c r="Z73" s="41"/>
       <c r="AA73" s="42"/>
       <c r="AB73" s="41"/>
       <c r="AC73" s="42"/>
-      <c r="AD73" s="47"/>
-      <c r="AE73" s="48"/>
+      <c r="AD73" s="43"/>
+      <c r="AE73" s="44"/>
       <c r="AF73" s="22"/>
       <c r="AG73" s="22"/>
       <c r="AH73" s="22"/>
@@ -3991,8 +3991,8 @@
       <c r="AA74" s="42"/>
       <c r="AB74" s="41"/>
       <c r="AC74" s="42"/>
-      <c r="AD74" s="47"/>
-      <c r="AE74" s="48"/>
+      <c r="AD74" s="43"/>
+      <c r="AE74" s="44"/>
       <c r="AF74" s="20"/>
       <c r="AG74" s="20"/>
       <c r="AH74" s="20"/>
@@ -4028,8 +4028,8 @@
       <c r="AA75" s="42"/>
       <c r="AB75" s="41"/>
       <c r="AC75" s="42"/>
-      <c r="AD75" s="47"/>
-      <c r="AE75" s="48"/>
+      <c r="AD75" s="43"/>
+      <c r="AE75" s="44"/>
       <c r="AF75" s="1"/>
       <c r="AG75" s="20"/>
       <c r="AH75" s="20"/>
@@ -4061,12 +4061,12 @@
       <c r="W76" s="42"/>
       <c r="X76" s="41"/>
       <c r="Y76" s="42"/>
-      <c r="Z76" s="47"/>
-      <c r="AA76" s="48"/>
-      <c r="AB76" s="47"/>
-      <c r="AC76" s="48"/>
-      <c r="AD76" s="47"/>
-      <c r="AE76" s="48"/>
+      <c r="Z76" s="43"/>
+      <c r="AA76" s="44"/>
+      <c r="AB76" s="43"/>
+      <c r="AC76" s="44"/>
+      <c r="AD76" s="43"/>
+      <c r="AE76" s="44"/>
       <c r="AF76" s="20"/>
       <c r="AG76" s="20"/>
       <c r="AH76" s="20"/>
@@ -4090,20 +4090,20 @@
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="3"/>
-      <c r="R77" s="47"/>
-      <c r="S77" s="48"/>
-      <c r="T77" s="47"/>
-      <c r="U77" s="48"/>
-      <c r="V77" s="47"/>
-      <c r="W77" s="48"/>
-      <c r="X77" s="47"/>
-      <c r="Y77" s="48"/>
-      <c r="Z77" s="47"/>
-      <c r="AA77" s="48"/>
-      <c r="AB77" s="47"/>
-      <c r="AC77" s="48"/>
-      <c r="AD77" s="47"/>
-      <c r="AE77" s="48"/>
+      <c r="R77" s="43"/>
+      <c r="S77" s="44"/>
+      <c r="T77" s="43"/>
+      <c r="U77" s="44"/>
+      <c r="V77" s="43"/>
+      <c r="W77" s="44"/>
+      <c r="X77" s="43"/>
+      <c r="Y77" s="44"/>
+      <c r="Z77" s="43"/>
+      <c r="AA77" s="44"/>
+      <c r="AB77" s="43"/>
+      <c r="AC77" s="44"/>
+      <c r="AD77" s="43"/>
+      <c r="AE77" s="44"/>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1"/>
       <c r="AH77" s="22"/>
@@ -4127,20 +4127,20 @@
       <c r="O78" s="5"/>
       <c r="P78" s="26"/>
       <c r="Q78" s="3"/>
-      <c r="R78" s="51"/>
-      <c r="S78" s="52"/>
-      <c r="T78" s="51"/>
-      <c r="U78" s="52"/>
-      <c r="V78" s="51"/>
-      <c r="W78" s="52"/>
+      <c r="R78" s="48"/>
+      <c r="S78" s="49"/>
+      <c r="T78" s="48"/>
+      <c r="U78" s="49"/>
+      <c r="V78" s="48"/>
+      <c r="W78" s="49"/>
       <c r="X78" s="41"/>
       <c r="Y78" s="42"/>
       <c r="Z78" s="41"/>
       <c r="AA78" s="42"/>
       <c r="AB78" s="41"/>
       <c r="AC78" s="42"/>
-      <c r="AD78" s="47"/>
-      <c r="AE78" s="48"/>
+      <c r="AD78" s="43"/>
+      <c r="AE78" s="44"/>
       <c r="AF78" s="20"/>
       <c r="AG78" s="1"/>
       <c r="AH78" s="22"/>
@@ -4164,20 +4164,20 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="3"/>
-      <c r="R79" s="51"/>
-      <c r="S79" s="52"/>
-      <c r="T79" s="51"/>
-      <c r="U79" s="52"/>
-      <c r="V79" s="51"/>
-      <c r="W79" s="52"/>
-      <c r="X79" s="47"/>
-      <c r="Y79" s="48"/>
+      <c r="R79" s="48"/>
+      <c r="S79" s="49"/>
+      <c r="T79" s="48"/>
+      <c r="U79" s="49"/>
+      <c r="V79" s="48"/>
+      <c r="W79" s="49"/>
+      <c r="X79" s="43"/>
+      <c r="Y79" s="44"/>
       <c r="Z79" s="41"/>
       <c r="AA79" s="42"/>
       <c r="AB79" s="41"/>
       <c r="AC79" s="42"/>
-      <c r="AD79" s="47"/>
-      <c r="AE79" s="48"/>
+      <c r="AD79" s="43"/>
+      <c r="AE79" s="44"/>
       <c r="AF79" s="20"/>
       <c r="AG79" s="22"/>
       <c r="AH79" s="22"/>
@@ -4201,20 +4201,20 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="3"/>
-      <c r="R80" s="51"/>
-      <c r="S80" s="52"/>
-      <c r="T80" s="51"/>
-      <c r="U80" s="52"/>
-      <c r="V80" s="51"/>
-      <c r="W80" s="52"/>
+      <c r="R80" s="48"/>
+      <c r="S80" s="49"/>
+      <c r="T80" s="48"/>
+      <c r="U80" s="49"/>
+      <c r="V80" s="48"/>
+      <c r="W80" s="49"/>
       <c r="X80" s="41"/>
       <c r="Y80" s="42"/>
       <c r="Z80" s="41"/>
       <c r="AA80" s="42"/>
       <c r="AB80" s="41"/>
       <c r="AC80" s="42"/>
-      <c r="AD80" s="47"/>
-      <c r="AE80" s="48"/>
+      <c r="AD80" s="43"/>
+      <c r="AE80" s="44"/>
       <c r="AF80" s="20"/>
       <c r="AG80" s="22"/>
       <c r="AH80" s="22"/>
@@ -4238,20 +4238,20 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
       <c r="Q81" s="3"/>
-      <c r="R81" s="51"/>
-      <c r="S81" s="52"/>
-      <c r="T81" s="51"/>
-      <c r="U81" s="52"/>
-      <c r="V81" s="51"/>
-      <c r="W81" s="52"/>
+      <c r="R81" s="48"/>
+      <c r="S81" s="49"/>
+      <c r="T81" s="48"/>
+      <c r="U81" s="49"/>
+      <c r="V81" s="48"/>
+      <c r="W81" s="49"/>
       <c r="X81" s="41"/>
       <c r="Y81" s="42"/>
       <c r="Z81" s="41"/>
       <c r="AA81" s="42"/>
       <c r="AB81" s="41"/>
       <c r="AC81" s="42"/>
-      <c r="AD81" s="47"/>
-      <c r="AE81" s="48"/>
+      <c r="AD81" s="43"/>
+      <c r="AE81" s="44"/>
       <c r="AF81" s="20"/>
       <c r="AG81" s="20"/>
       <c r="AH81" s="20"/>
@@ -4275,20 +4275,20 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
       <c r="Q82" s="3"/>
-      <c r="R82" s="51"/>
-      <c r="S82" s="52"/>
-      <c r="T82" s="49"/>
-      <c r="U82" s="50"/>
-      <c r="V82" s="49"/>
-      <c r="W82" s="50"/>
-      <c r="X82" s="47"/>
-      <c r="Y82" s="48"/>
-      <c r="Z82" s="47"/>
-      <c r="AA82" s="48"/>
-      <c r="AB82" s="47"/>
-      <c r="AC82" s="48"/>
-      <c r="AD82" s="47"/>
-      <c r="AE82" s="48"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="49"/>
+      <c r="T82" s="50"/>
+      <c r="U82" s="51"/>
+      <c r="V82" s="50"/>
+      <c r="W82" s="51"/>
+      <c r="X82" s="43"/>
+      <c r="Y82" s="44"/>
+      <c r="Z82" s="43"/>
+      <c r="AA82" s="44"/>
+      <c r="AB82" s="43"/>
+      <c r="AC82" s="44"/>
+      <c r="AD82" s="43"/>
+      <c r="AE82" s="44"/>
       <c r="AF82" s="1"/>
       <c r="AG82" s="1"/>
       <c r="AH82" s="22"/>
@@ -4312,20 +4312,20 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
       <c r="Q83" s="3"/>
-      <c r="R83" s="51"/>
-      <c r="S83" s="52"/>
-      <c r="T83" s="51"/>
-      <c r="U83" s="52"/>
-      <c r="V83" s="51"/>
-      <c r="W83" s="52"/>
+      <c r="R83" s="48"/>
+      <c r="S83" s="49"/>
+      <c r="T83" s="48"/>
+      <c r="U83" s="49"/>
+      <c r="V83" s="48"/>
+      <c r="W83" s="49"/>
       <c r="X83" s="41"/>
       <c r="Y83" s="42"/>
       <c r="Z83" s="41"/>
       <c r="AA83" s="42"/>
       <c r="AB83" s="41"/>
       <c r="AC83" s="42"/>
-      <c r="AD83" s="47"/>
-      <c r="AE83" s="48"/>
+      <c r="AD83" s="43"/>
+      <c r="AE83" s="44"/>
       <c r="AF83" s="20"/>
       <c r="AG83" s="20"/>
       <c r="AH83" s="20"/>
@@ -4349,20 +4349,20 @@
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
       <c r="Q84" s="3"/>
-      <c r="R84" s="51"/>
-      <c r="S84" s="52"/>
-      <c r="T84" s="51"/>
-      <c r="U84" s="52"/>
-      <c r="V84" s="51"/>
-      <c r="W84" s="52"/>
+      <c r="R84" s="48"/>
+      <c r="S84" s="49"/>
+      <c r="T84" s="48"/>
+      <c r="U84" s="49"/>
+      <c r="V84" s="48"/>
+      <c r="W84" s="49"/>
       <c r="X84" s="41"/>
       <c r="Y84" s="42"/>
       <c r="Z84" s="41"/>
       <c r="AA84" s="42"/>
       <c r="AB84" s="41"/>
       <c r="AC84" s="42"/>
-      <c r="AD84" s="47"/>
-      <c r="AE84" s="48"/>
+      <c r="AD84" s="43"/>
+      <c r="AE84" s="44"/>
       <c r="AF84" s="20"/>
       <c r="AG84" s="20"/>
       <c r="AH84" s="20"/>
@@ -4386,20 +4386,20 @@
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="3"/>
-      <c r="R85" s="51"/>
-      <c r="S85" s="52"/>
-      <c r="T85" s="51"/>
-      <c r="U85" s="52"/>
-      <c r="V85" s="51"/>
-      <c r="W85" s="52"/>
+      <c r="R85" s="48"/>
+      <c r="S85" s="49"/>
+      <c r="T85" s="48"/>
+      <c r="U85" s="49"/>
+      <c r="V85" s="48"/>
+      <c r="W85" s="49"/>
       <c r="X85" s="41"/>
       <c r="Y85" s="42"/>
       <c r="Z85" s="41"/>
       <c r="AA85" s="42"/>
       <c r="AB85" s="41"/>
       <c r="AC85" s="42"/>
-      <c r="AD85" s="47"/>
-      <c r="AE85" s="48"/>
+      <c r="AD85" s="43"/>
+      <c r="AE85" s="44"/>
       <c r="AF85" s="20"/>
       <c r="AG85" s="20"/>
       <c r="AH85" s="20"/>
@@ -4423,20 +4423,20 @@
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="3"/>
-      <c r="R86" s="51"/>
-      <c r="S86" s="52"/>
-      <c r="T86" s="51"/>
-      <c r="U86" s="52"/>
-      <c r="V86" s="51"/>
-      <c r="W86" s="52"/>
+      <c r="R86" s="48"/>
+      <c r="S86" s="49"/>
+      <c r="T86" s="48"/>
+      <c r="U86" s="49"/>
+      <c r="V86" s="48"/>
+      <c r="W86" s="49"/>
       <c r="X86" s="41"/>
       <c r="Y86" s="42"/>
       <c r="Z86" s="41"/>
       <c r="AA86" s="42"/>
       <c r="AB86" s="41"/>
       <c r="AC86" s="42"/>
-      <c r="AD86" s="47"/>
-      <c r="AE86" s="48"/>
+      <c r="AD86" s="43"/>
+      <c r="AE86" s="44"/>
       <c r="AF86" s="1"/>
       <c r="AG86" s="20"/>
       <c r="AH86" s="20"/>
@@ -4460,20 +4460,20 @@
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="3"/>
-      <c r="R87" s="51"/>
-      <c r="S87" s="52"/>
-      <c r="T87" s="51"/>
-      <c r="U87" s="52"/>
-      <c r="V87" s="51"/>
-      <c r="W87" s="52"/>
+      <c r="R87" s="48"/>
+      <c r="S87" s="49"/>
+      <c r="T87" s="48"/>
+      <c r="U87" s="49"/>
+      <c r="V87" s="48"/>
+      <c r="W87" s="49"/>
       <c r="X87" s="41"/>
       <c r="Y87" s="42"/>
       <c r="Z87" s="41"/>
       <c r="AA87" s="42"/>
       <c r="AB87" s="41"/>
       <c r="AC87" s="42"/>
-      <c r="AD87" s="47"/>
-      <c r="AE87" s="48"/>
+      <c r="AD87" s="43"/>
+      <c r="AE87" s="44"/>
       <c r="AF87" s="20"/>
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
@@ -4497,20 +4497,20 @@
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
-      <c r="R88" s="51"/>
-      <c r="S88" s="52"/>
-      <c r="T88" s="51"/>
-      <c r="U88" s="52"/>
-      <c r="V88" s="51"/>
-      <c r="W88" s="52"/>
+      <c r="R88" s="48"/>
+      <c r="S88" s="49"/>
+      <c r="T88" s="48"/>
+      <c r="U88" s="49"/>
+      <c r="V88" s="48"/>
+      <c r="W88" s="49"/>
       <c r="X88" s="41"/>
       <c r="Y88" s="42"/>
       <c r="Z88" s="41"/>
       <c r="AA88" s="42"/>
       <c r="AB88" s="41"/>
       <c r="AC88" s="42"/>
-      <c r="AD88" s="47"/>
-      <c r="AE88" s="48"/>
+      <c r="AD88" s="43"/>
+      <c r="AE88" s="44"/>
       <c r="AF88" s="20"/>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
@@ -4534,20 +4534,20 @@
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="6"/>
-      <c r="R89" s="51"/>
-      <c r="S89" s="52"/>
-      <c r="T89" s="51"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="51"/>
-      <c r="W89" s="52"/>
+      <c r="R89" s="48"/>
+      <c r="S89" s="49"/>
+      <c r="T89" s="48"/>
+      <c r="U89" s="49"/>
+      <c r="V89" s="48"/>
+      <c r="W89" s="49"/>
       <c r="X89" s="41"/>
       <c r="Y89" s="42"/>
       <c r="Z89" s="41"/>
       <c r="AA89" s="42"/>
       <c r="AB89" s="41"/>
       <c r="AC89" s="42"/>
-      <c r="AD89" s="47"/>
-      <c r="AE89" s="48"/>
+      <c r="AD89" s="43"/>
+      <c r="AE89" s="44"/>
       <c r="AF89" s="20"/>
       <c r="AG89" s="1"/>
       <c r="AH89" s="22"/>
@@ -4571,20 +4571,20 @@
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="3"/>
-      <c r="R90" s="49"/>
-      <c r="S90" s="50"/>
-      <c r="T90" s="49"/>
-      <c r="U90" s="50"/>
-      <c r="V90" s="49"/>
-      <c r="W90" s="50"/>
-      <c r="X90" s="47"/>
-      <c r="Y90" s="48"/>
-      <c r="Z90" s="47"/>
-      <c r="AA90" s="48"/>
-      <c r="AB90" s="47"/>
-      <c r="AC90" s="48"/>
-      <c r="AD90" s="47"/>
-      <c r="AE90" s="48"/>
+      <c r="R90" s="50"/>
+      <c r="S90" s="51"/>
+      <c r="T90" s="50"/>
+      <c r="U90" s="51"/>
+      <c r="V90" s="50"/>
+      <c r="W90" s="51"/>
+      <c r="X90" s="43"/>
+      <c r="Y90" s="44"/>
+      <c r="Z90" s="43"/>
+      <c r="AA90" s="44"/>
+      <c r="AB90" s="43"/>
+      <c r="AC90" s="44"/>
+      <c r="AD90" s="43"/>
+      <c r="AE90" s="44"/>
       <c r="AF90" s="1"/>
       <c r="AG90" s="1"/>
       <c r="AH90" s="20"/>
@@ -4608,20 +4608,20 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="3"/>
-      <c r="R91" s="51"/>
-      <c r="S91" s="52"/>
-      <c r="T91" s="51"/>
-      <c r="U91" s="52"/>
-      <c r="V91" s="51"/>
-      <c r="W91" s="52"/>
+      <c r="R91" s="48"/>
+      <c r="S91" s="49"/>
+      <c r="T91" s="48"/>
+      <c r="U91" s="49"/>
+      <c r="V91" s="48"/>
+      <c r="W91" s="49"/>
       <c r="X91" s="41"/>
       <c r="Y91" s="42"/>
       <c r="Z91" s="41"/>
       <c r="AA91" s="42"/>
       <c r="AB91" s="41"/>
       <c r="AC91" s="42"/>
-      <c r="AD91" s="47"/>
-      <c r="AE91" s="48"/>
+      <c r="AD91" s="43"/>
+      <c r="AE91" s="44"/>
       <c r="AF91" s="20"/>
       <c r="AG91" s="27"/>
       <c r="AH91" s="20"/>
@@ -4645,20 +4645,20 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="3"/>
-      <c r="R92" s="49"/>
-      <c r="S92" s="50"/>
-      <c r="T92" s="49"/>
-      <c r="U92" s="50"/>
-      <c r="V92" s="49"/>
-      <c r="W92" s="50"/>
-      <c r="X92" s="47"/>
-      <c r="Y92" s="48"/>
-      <c r="Z92" s="47"/>
-      <c r="AA92" s="48"/>
-      <c r="AB92" s="47"/>
-      <c r="AC92" s="48"/>
-      <c r="AD92" s="47"/>
-      <c r="AE92" s="48"/>
+      <c r="R92" s="50"/>
+      <c r="S92" s="51"/>
+      <c r="T92" s="50"/>
+      <c r="U92" s="51"/>
+      <c r="V92" s="50"/>
+      <c r="W92" s="51"/>
+      <c r="X92" s="43"/>
+      <c r="Y92" s="44"/>
+      <c r="Z92" s="43"/>
+      <c r="AA92" s="44"/>
+      <c r="AB92" s="43"/>
+      <c r="AC92" s="44"/>
+      <c r="AD92" s="43"/>
+      <c r="AE92" s="44"/>
       <c r="AF92" s="1"/>
       <c r="AG92" s="22"/>
       <c r="AH92" s="22"/>
@@ -4682,20 +4682,20 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
-      <c r="R93" s="49"/>
-      <c r="S93" s="50"/>
-      <c r="T93" s="49"/>
-      <c r="U93" s="50"/>
-      <c r="V93" s="49"/>
-      <c r="W93" s="50"/>
-      <c r="X93" s="47"/>
-      <c r="Y93" s="48"/>
-      <c r="Z93" s="47"/>
-      <c r="AA93" s="48"/>
-      <c r="AB93" s="47"/>
-      <c r="AC93" s="48"/>
-      <c r="AD93" s="47"/>
-      <c r="AE93" s="48"/>
+      <c r="R93" s="50"/>
+      <c r="S93" s="51"/>
+      <c r="T93" s="50"/>
+      <c r="U93" s="51"/>
+      <c r="V93" s="50"/>
+      <c r="W93" s="51"/>
+      <c r="X93" s="43"/>
+      <c r="Y93" s="44"/>
+      <c r="Z93" s="43"/>
+      <c r="AA93" s="44"/>
+      <c r="AB93" s="43"/>
+      <c r="AC93" s="44"/>
+      <c r="AD93" s="43"/>
+      <c r="AE93" s="44"/>
       <c r="AF93" s="22"/>
       <c r="AG93" s="22"/>
       <c r="AH93" s="22"/>
@@ -4719,20 +4719,20 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
       <c r="Q94" s="3"/>
-      <c r="R94" s="49"/>
-      <c r="S94" s="50"/>
-      <c r="T94" s="49"/>
-      <c r="U94" s="50"/>
-      <c r="V94" s="49"/>
-      <c r="W94" s="50"/>
-      <c r="X94" s="47"/>
-      <c r="Y94" s="48"/>
-      <c r="Z94" s="47"/>
-      <c r="AA94" s="48"/>
-      <c r="AB94" s="47"/>
-      <c r="AC94" s="48"/>
-      <c r="AD94" s="47"/>
-      <c r="AE94" s="48"/>
+      <c r="R94" s="50"/>
+      <c r="S94" s="51"/>
+      <c r="T94" s="50"/>
+      <c r="U94" s="51"/>
+      <c r="V94" s="50"/>
+      <c r="W94" s="51"/>
+      <c r="X94" s="43"/>
+      <c r="Y94" s="44"/>
+      <c r="Z94" s="43"/>
+      <c r="AA94" s="44"/>
+      <c r="AB94" s="43"/>
+      <c r="AC94" s="44"/>
+      <c r="AD94" s="43"/>
+      <c r="AE94" s="44"/>
       <c r="AF94" s="1"/>
       <c r="AG94" s="22"/>
       <c r="AH94" s="22"/>
@@ -4756,20 +4756,20 @@
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
       <c r="Q95" s="3"/>
-      <c r="R95" s="49"/>
-      <c r="S95" s="50"/>
-      <c r="T95" s="49"/>
-      <c r="U95" s="50"/>
-      <c r="V95" s="49"/>
-      <c r="W95" s="50"/>
-      <c r="X95" s="47"/>
-      <c r="Y95" s="48"/>
-      <c r="Z95" s="47"/>
-      <c r="AA95" s="48"/>
-      <c r="AB95" s="47"/>
-      <c r="AC95" s="48"/>
-      <c r="AD95" s="47"/>
-      <c r="AE95" s="48"/>
+      <c r="R95" s="50"/>
+      <c r="S95" s="51"/>
+      <c r="T95" s="50"/>
+      <c r="U95" s="51"/>
+      <c r="V95" s="50"/>
+      <c r="W95" s="51"/>
+      <c r="X95" s="43"/>
+      <c r="Y95" s="44"/>
+      <c r="Z95" s="43"/>
+      <c r="AA95" s="44"/>
+      <c r="AB95" s="43"/>
+      <c r="AC95" s="44"/>
+      <c r="AD95" s="43"/>
+      <c r="AE95" s="44"/>
       <c r="AF95" s="22"/>
       <c r="AG95" s="22"/>
       <c r="AH95" s="22"/>
@@ -4793,20 +4793,20 @@
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="49"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="49"/>
-      <c r="U96" s="50"/>
-      <c r="V96" s="49"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="47"/>
-      <c r="Y96" s="48"/>
-      <c r="Z96" s="47"/>
-      <c r="AA96" s="48"/>
-      <c r="AB96" s="47"/>
-      <c r="AC96" s="48"/>
-      <c r="AD96" s="47"/>
-      <c r="AE96" s="48"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="51"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="51"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="51"/>
+      <c r="X96" s="43"/>
+      <c r="Y96" s="44"/>
+      <c r="Z96" s="43"/>
+      <c r="AA96" s="44"/>
+      <c r="AB96" s="43"/>
+      <c r="AC96" s="44"/>
+      <c r="AD96" s="43"/>
+      <c r="AE96" s="44"/>
       <c r="AF96" s="1"/>
       <c r="AG96" s="22"/>
       <c r="AH96" s="22"/>
@@ -4830,20 +4830,20 @@
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
-      <c r="R97" s="49"/>
-      <c r="S97" s="50"/>
-      <c r="T97" s="49"/>
-      <c r="U97" s="50"/>
-      <c r="V97" s="49"/>
-      <c r="W97" s="50"/>
-      <c r="X97" s="47"/>
-      <c r="Y97" s="48"/>
-      <c r="Z97" s="47"/>
-      <c r="AA97" s="48"/>
-      <c r="AB97" s="47"/>
-      <c r="AC97" s="48"/>
-      <c r="AD97" s="47"/>
-      <c r="AE97" s="48"/>
+      <c r="R97" s="50"/>
+      <c r="S97" s="51"/>
+      <c r="T97" s="50"/>
+      <c r="U97" s="51"/>
+      <c r="V97" s="50"/>
+      <c r="W97" s="51"/>
+      <c r="X97" s="43"/>
+      <c r="Y97" s="44"/>
+      <c r="Z97" s="43"/>
+      <c r="AA97" s="44"/>
+      <c r="AB97" s="43"/>
+      <c r="AC97" s="44"/>
+      <c r="AD97" s="43"/>
+      <c r="AE97" s="44"/>
       <c r="AF97" s="1"/>
       <c r="AG97" s="22"/>
       <c r="AH97" s="22"/>
@@ -4867,20 +4867,20 @@
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="49"/>
-      <c r="S98" s="50"/>
-      <c r="T98" s="49"/>
-      <c r="U98" s="50"/>
-      <c r="V98" s="49"/>
-      <c r="W98" s="50"/>
-      <c r="X98" s="47"/>
-      <c r="Y98" s="48"/>
-      <c r="Z98" s="47"/>
-      <c r="AA98" s="48"/>
-      <c r="AB98" s="47"/>
-      <c r="AC98" s="48"/>
-      <c r="AD98" s="47"/>
-      <c r="AE98" s="48"/>
+      <c r="R98" s="50"/>
+      <c r="S98" s="51"/>
+      <c r="T98" s="50"/>
+      <c r="U98" s="51"/>
+      <c r="V98" s="50"/>
+      <c r="W98" s="51"/>
+      <c r="X98" s="43"/>
+      <c r="Y98" s="44"/>
+      <c r="Z98" s="43"/>
+      <c r="AA98" s="44"/>
+      <c r="AB98" s="43"/>
+      <c r="AC98" s="44"/>
+      <c r="AD98" s="43"/>
+      <c r="AE98" s="44"/>
       <c r="AF98" s="1"/>
       <c r="AG98" s="1"/>
       <c r="AH98" s="22"/>
@@ -4904,20 +4904,20 @@
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="3"/>
-      <c r="R99" s="49"/>
-      <c r="S99" s="50"/>
-      <c r="T99" s="49"/>
-      <c r="U99" s="50"/>
-      <c r="V99" s="49"/>
-      <c r="W99" s="50"/>
-      <c r="X99" s="47"/>
-      <c r="Y99" s="48"/>
-      <c r="Z99" s="47"/>
-      <c r="AA99" s="48"/>
-      <c r="AB99" s="47"/>
-      <c r="AC99" s="48"/>
-      <c r="AD99" s="47"/>
-      <c r="AE99" s="48"/>
+      <c r="R99" s="50"/>
+      <c r="S99" s="51"/>
+      <c r="T99" s="50"/>
+      <c r="U99" s="51"/>
+      <c r="V99" s="50"/>
+      <c r="W99" s="51"/>
+      <c r="X99" s="43"/>
+      <c r="Y99" s="44"/>
+      <c r="Z99" s="43"/>
+      <c r="AA99" s="44"/>
+      <c r="AB99" s="43"/>
+      <c r="AC99" s="44"/>
+      <c r="AD99" s="43"/>
+      <c r="AE99" s="44"/>
       <c r="AF99" s="22"/>
       <c r="AG99" s="22"/>
       <c r="AH99" s="22"/>
@@ -4941,20 +4941,20 @@
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="3"/>
-      <c r="R100" s="49"/>
-      <c r="S100" s="50"/>
-      <c r="T100" s="49"/>
-      <c r="U100" s="50"/>
-      <c r="V100" s="49"/>
-      <c r="W100" s="50"/>
-      <c r="X100" s="47"/>
-      <c r="Y100" s="48"/>
-      <c r="Z100" s="47"/>
-      <c r="AA100" s="48"/>
-      <c r="AB100" s="47"/>
-      <c r="AC100" s="48"/>
-      <c r="AD100" s="47"/>
-      <c r="AE100" s="48"/>
+      <c r="R100" s="50"/>
+      <c r="S100" s="51"/>
+      <c r="T100" s="50"/>
+      <c r="U100" s="51"/>
+      <c r="V100" s="50"/>
+      <c r="W100" s="51"/>
+      <c r="X100" s="43"/>
+      <c r="Y100" s="44"/>
+      <c r="Z100" s="43"/>
+      <c r="AA100" s="44"/>
+      <c r="AB100" s="43"/>
+      <c r="AC100" s="44"/>
+      <c r="AD100" s="43"/>
+      <c r="AE100" s="44"/>
       <c r="AF100" s="22"/>
       <c r="AG100" s="1"/>
       <c r="AH100" s="22"/>
@@ -4978,20 +4978,20 @@
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="3"/>
-      <c r="R101" s="49"/>
-      <c r="S101" s="50"/>
-      <c r="T101" s="49"/>
-      <c r="U101" s="50"/>
-      <c r="V101" s="49"/>
-      <c r="W101" s="50"/>
-      <c r="X101" s="47"/>
-      <c r="Y101" s="48"/>
-      <c r="Z101" s="47"/>
-      <c r="AA101" s="48"/>
-      <c r="AB101" s="47"/>
-      <c r="AC101" s="48"/>
-      <c r="AD101" s="47"/>
-      <c r="AE101" s="48"/>
+      <c r="R101" s="50"/>
+      <c r="S101" s="51"/>
+      <c r="T101" s="50"/>
+      <c r="U101" s="51"/>
+      <c r="V101" s="50"/>
+      <c r="W101" s="51"/>
+      <c r="X101" s="43"/>
+      <c r="Y101" s="44"/>
+      <c r="Z101" s="43"/>
+      <c r="AA101" s="44"/>
+      <c r="AB101" s="43"/>
+      <c r="AC101" s="44"/>
+      <c r="AD101" s="43"/>
+      <c r="AE101" s="44"/>
       <c r="AF101" s="22"/>
       <c r="AG101" s="22"/>
       <c r="AH101" s="22"/>
@@ -5015,20 +5015,20 @@
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="3"/>
-      <c r="R102" s="49"/>
-      <c r="S102" s="50"/>
-      <c r="T102" s="49"/>
-      <c r="U102" s="50"/>
-      <c r="V102" s="49"/>
-      <c r="W102" s="50"/>
-      <c r="X102" s="47"/>
-      <c r="Y102" s="48"/>
-      <c r="Z102" s="47"/>
-      <c r="AA102" s="48"/>
-      <c r="AB102" s="47"/>
-      <c r="AC102" s="48"/>
-      <c r="AD102" s="47"/>
-      <c r="AE102" s="48"/>
+      <c r="R102" s="50"/>
+      <c r="S102" s="51"/>
+      <c r="T102" s="50"/>
+      <c r="U102" s="51"/>
+      <c r="V102" s="50"/>
+      <c r="W102" s="51"/>
+      <c r="X102" s="43"/>
+      <c r="Y102" s="44"/>
+      <c r="Z102" s="43"/>
+      <c r="AA102" s="44"/>
+      <c r="AB102" s="43"/>
+      <c r="AC102" s="44"/>
+      <c r="AD102" s="43"/>
+      <c r="AE102" s="44"/>
       <c r="AF102" s="1"/>
       <c r="AG102" s="22"/>
       <c r="AH102" s="22"/>
@@ -5052,20 +5052,20 @@
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="3"/>
-      <c r="R103" s="49"/>
-      <c r="S103" s="50"/>
-      <c r="T103" s="49"/>
-      <c r="U103" s="50"/>
-      <c r="V103" s="49"/>
-      <c r="W103" s="50"/>
-      <c r="X103" s="47"/>
-      <c r="Y103" s="48"/>
-      <c r="Z103" s="47"/>
-      <c r="AA103" s="48"/>
-      <c r="AB103" s="47"/>
-      <c r="AC103" s="48"/>
-      <c r="AD103" s="47"/>
-      <c r="AE103" s="48"/>
+      <c r="R103" s="50"/>
+      <c r="S103" s="51"/>
+      <c r="T103" s="50"/>
+      <c r="U103" s="51"/>
+      <c r="V103" s="50"/>
+      <c r="W103" s="51"/>
+      <c r="X103" s="43"/>
+      <c r="Y103" s="44"/>
+      <c r="Z103" s="43"/>
+      <c r="AA103" s="44"/>
+      <c r="AB103" s="43"/>
+      <c r="AC103" s="44"/>
+      <c r="AD103" s="43"/>
+      <c r="AE103" s="44"/>
       <c r="AF103" s="1"/>
       <c r="AG103" s="22"/>
       <c r="AH103" s="22"/>
@@ -5089,20 +5089,20 @@
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="3"/>
-      <c r="R104" s="49"/>
-      <c r="S104" s="50"/>
-      <c r="T104" s="49"/>
-      <c r="U104" s="50"/>
-      <c r="V104" s="49"/>
-      <c r="W104" s="50"/>
-      <c r="X104" s="47"/>
-      <c r="Y104" s="48"/>
-      <c r="Z104" s="47"/>
-      <c r="AA104" s="48"/>
-      <c r="AB104" s="47"/>
-      <c r="AC104" s="48"/>
-      <c r="AD104" s="47"/>
-      <c r="AE104" s="48"/>
+      <c r="R104" s="50"/>
+      <c r="S104" s="51"/>
+      <c r="T104" s="50"/>
+      <c r="U104" s="51"/>
+      <c r="V104" s="50"/>
+      <c r="W104" s="51"/>
+      <c r="X104" s="43"/>
+      <c r="Y104" s="44"/>
+      <c r="Z104" s="43"/>
+      <c r="AA104" s="44"/>
+      <c r="AB104" s="43"/>
+      <c r="AC104" s="44"/>
+      <c r="AD104" s="43"/>
+      <c r="AE104" s="44"/>
       <c r="AF104" s="1"/>
       <c r="AG104" s="22"/>
       <c r="AH104" s="22"/>
@@ -5126,20 +5126,20 @@
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="3"/>
-      <c r="R105" s="49"/>
-      <c r="S105" s="50"/>
-      <c r="T105" s="49"/>
-      <c r="U105" s="50"/>
-      <c r="V105" s="49"/>
-      <c r="W105" s="50"/>
-      <c r="X105" s="47"/>
-      <c r="Y105" s="48"/>
-      <c r="Z105" s="47"/>
-      <c r="AA105" s="48"/>
-      <c r="AB105" s="47"/>
-      <c r="AC105" s="48"/>
-      <c r="AD105" s="47"/>
-      <c r="AE105" s="48"/>
+      <c r="R105" s="50"/>
+      <c r="S105" s="51"/>
+      <c r="T105" s="50"/>
+      <c r="U105" s="51"/>
+      <c r="V105" s="50"/>
+      <c r="W105" s="51"/>
+      <c r="X105" s="43"/>
+      <c r="Y105" s="44"/>
+      <c r="Z105" s="43"/>
+      <c r="AA105" s="44"/>
+      <c r="AB105" s="43"/>
+      <c r="AC105" s="44"/>
+      <c r="AD105" s="43"/>
+      <c r="AE105" s="44"/>
       <c r="AF105" s="22"/>
       <c r="AG105" s="22"/>
       <c r="AH105" s="22"/>
@@ -5163,20 +5163,20 @@
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="3"/>
-      <c r="R106" s="49"/>
-      <c r="S106" s="50"/>
-      <c r="T106" s="49"/>
-      <c r="U106" s="50"/>
-      <c r="V106" s="49"/>
-      <c r="W106" s="50"/>
-      <c r="X106" s="47"/>
-      <c r="Y106" s="48"/>
-      <c r="Z106" s="47"/>
-      <c r="AA106" s="48"/>
-      <c r="AB106" s="47"/>
-      <c r="AC106" s="48"/>
-      <c r="AD106" s="47"/>
-      <c r="AE106" s="48"/>
+      <c r="R106" s="50"/>
+      <c r="S106" s="51"/>
+      <c r="T106" s="50"/>
+      <c r="U106" s="51"/>
+      <c r="V106" s="50"/>
+      <c r="W106" s="51"/>
+      <c r="X106" s="43"/>
+      <c r="Y106" s="44"/>
+      <c r="Z106" s="43"/>
+      <c r="AA106" s="44"/>
+      <c r="AB106" s="43"/>
+      <c r="AC106" s="44"/>
+      <c r="AD106" s="43"/>
+      <c r="AE106" s="44"/>
       <c r="AF106" s="1"/>
       <c r="AG106" s="1"/>
       <c r="AH106" s="22"/>
@@ -5200,20 +5200,20 @@
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="3"/>
-      <c r="R107" s="49"/>
-      <c r="S107" s="50"/>
-      <c r="T107" s="49"/>
-      <c r="U107" s="50"/>
-      <c r="V107" s="49"/>
-      <c r="W107" s="50"/>
-      <c r="X107" s="47"/>
-      <c r="Y107" s="48"/>
-      <c r="Z107" s="47"/>
-      <c r="AA107" s="48"/>
-      <c r="AB107" s="47"/>
-      <c r="AC107" s="48"/>
-      <c r="AD107" s="47"/>
-      <c r="AE107" s="48"/>
+      <c r="R107" s="50"/>
+      <c r="S107" s="51"/>
+      <c r="T107" s="50"/>
+      <c r="U107" s="51"/>
+      <c r="V107" s="50"/>
+      <c r="W107" s="51"/>
+      <c r="X107" s="43"/>
+      <c r="Y107" s="44"/>
+      <c r="Z107" s="43"/>
+      <c r="AA107" s="44"/>
+      <c r="AB107" s="43"/>
+      <c r="AC107" s="44"/>
+      <c r="AD107" s="43"/>
+      <c r="AE107" s="44"/>
       <c r="AF107" s="22"/>
       <c r="AG107" s="22"/>
       <c r="AH107" s="22"/>
@@ -5237,20 +5237,20 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
       <c r="Q108" s="3"/>
-      <c r="R108" s="49"/>
-      <c r="S108" s="50"/>
-      <c r="T108" s="49"/>
-      <c r="U108" s="50"/>
-      <c r="V108" s="49"/>
-      <c r="W108" s="50"/>
-      <c r="X108" s="47"/>
-      <c r="Y108" s="48"/>
-      <c r="Z108" s="47"/>
-      <c r="AA108" s="48"/>
-      <c r="AB108" s="47"/>
-      <c r="AC108" s="48"/>
-      <c r="AD108" s="47"/>
-      <c r="AE108" s="48"/>
+      <c r="R108" s="50"/>
+      <c r="S108" s="51"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="51"/>
+      <c r="V108" s="50"/>
+      <c r="W108" s="51"/>
+      <c r="X108" s="43"/>
+      <c r="Y108" s="44"/>
+      <c r="Z108" s="43"/>
+      <c r="AA108" s="44"/>
+      <c r="AB108" s="43"/>
+      <c r="AC108" s="44"/>
+      <c r="AD108" s="43"/>
+      <c r="AE108" s="44"/>
       <c r="AF108" s="22"/>
       <c r="AG108" s="1"/>
       <c r="AH108" s="22"/>
@@ -5274,20 +5274,20 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
       <c r="Q109" s="3"/>
-      <c r="R109" s="49"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="49"/>
-      <c r="U109" s="50"/>
-      <c r="V109" s="49"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="47"/>
-      <c r="Y109" s="48"/>
-      <c r="Z109" s="47"/>
-      <c r="AA109" s="48"/>
-      <c r="AB109" s="47"/>
-      <c r="AC109" s="48"/>
-      <c r="AD109" s="47"/>
-      <c r="AE109" s="48"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="51"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="51"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="51"/>
+      <c r="X109" s="43"/>
+      <c r="Y109" s="44"/>
+      <c r="Z109" s="43"/>
+      <c r="AA109" s="44"/>
+      <c r="AB109" s="43"/>
+      <c r="AC109" s="44"/>
+      <c r="AD109" s="43"/>
+      <c r="AE109" s="44"/>
       <c r="AF109" s="1"/>
       <c r="AG109" s="22"/>
       <c r="AH109" s="22"/>
@@ -5311,20 +5311,20 @@
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
       <c r="Q110" s="3"/>
-      <c r="R110" s="49"/>
-      <c r="S110" s="50"/>
-      <c r="T110" s="49"/>
-      <c r="U110" s="50"/>
-      <c r="V110" s="49"/>
-      <c r="W110" s="50"/>
-      <c r="X110" s="47"/>
-      <c r="Y110" s="48"/>
-      <c r="Z110" s="47"/>
-      <c r="AA110" s="48"/>
-      <c r="AB110" s="47"/>
-      <c r="AC110" s="48"/>
-      <c r="AD110" s="47"/>
-      <c r="AE110" s="48"/>
+      <c r="R110" s="50"/>
+      <c r="S110" s="51"/>
+      <c r="T110" s="50"/>
+      <c r="U110" s="51"/>
+      <c r="V110" s="50"/>
+      <c r="W110" s="51"/>
+      <c r="X110" s="43"/>
+      <c r="Y110" s="44"/>
+      <c r="Z110" s="43"/>
+      <c r="AA110" s="44"/>
+      <c r="AB110" s="43"/>
+      <c r="AC110" s="44"/>
+      <c r="AD110" s="43"/>
+      <c r="AE110" s="44"/>
       <c r="AF110" s="1"/>
       <c r="AG110" s="22"/>
       <c r="AH110" s="22"/>
@@ -5348,20 +5348,20 @@
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
       <c r="Q111" s="3"/>
-      <c r="R111" s="49"/>
-      <c r="S111" s="50"/>
-      <c r="T111" s="49"/>
-      <c r="U111" s="50"/>
-      <c r="V111" s="49"/>
-      <c r="W111" s="50"/>
-      <c r="X111" s="47"/>
-      <c r="Y111" s="48"/>
-      <c r="Z111" s="47"/>
-      <c r="AA111" s="48"/>
-      <c r="AB111" s="47"/>
-      <c r="AC111" s="48"/>
-      <c r="AD111" s="47"/>
-      <c r="AE111" s="48"/>
+      <c r="R111" s="50"/>
+      <c r="S111" s="51"/>
+      <c r="T111" s="50"/>
+      <c r="U111" s="51"/>
+      <c r="V111" s="50"/>
+      <c r="W111" s="51"/>
+      <c r="X111" s="43"/>
+      <c r="Y111" s="44"/>
+      <c r="Z111" s="43"/>
+      <c r="AA111" s="44"/>
+      <c r="AB111" s="43"/>
+      <c r="AC111" s="44"/>
+      <c r="AD111" s="43"/>
+      <c r="AE111" s="44"/>
       <c r="AF111" s="1"/>
       <c r="AG111" s="22"/>
       <c r="AH111" s="22"/>
@@ -5385,20 +5385,20 @@
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
-      <c r="R112" s="49"/>
-      <c r="S112" s="50"/>
-      <c r="T112" s="49"/>
-      <c r="U112" s="50"/>
-      <c r="V112" s="49"/>
-      <c r="W112" s="50"/>
-      <c r="X112" s="47"/>
-      <c r="Y112" s="48"/>
-      <c r="Z112" s="47"/>
-      <c r="AA112" s="48"/>
-      <c r="AB112" s="47"/>
-      <c r="AC112" s="48"/>
-      <c r="AD112" s="47"/>
-      <c r="AE112" s="48"/>
+      <c r="R112" s="50"/>
+      <c r="S112" s="51"/>
+      <c r="T112" s="50"/>
+      <c r="U112" s="51"/>
+      <c r="V112" s="50"/>
+      <c r="W112" s="51"/>
+      <c r="X112" s="43"/>
+      <c r="Y112" s="44"/>
+      <c r="Z112" s="43"/>
+      <c r="AA112" s="44"/>
+      <c r="AB112" s="43"/>
+      <c r="AC112" s="44"/>
+      <c r="AD112" s="43"/>
+      <c r="AE112" s="44"/>
       <c r="AF112" s="1"/>
       <c r="AG112" s="22"/>
       <c r="AH112" s="22"/>
@@ -5422,20 +5422,20 @@
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
       <c r="Q113" s="3"/>
-      <c r="R113" s="49"/>
-      <c r="S113" s="50"/>
-      <c r="T113" s="49"/>
-      <c r="U113" s="50"/>
-      <c r="V113" s="49"/>
-      <c r="W113" s="50"/>
-      <c r="X113" s="47"/>
-      <c r="Y113" s="48"/>
-      <c r="Z113" s="47"/>
-      <c r="AA113" s="48"/>
-      <c r="AB113" s="47"/>
-      <c r="AC113" s="48"/>
-      <c r="AD113" s="47"/>
-      <c r="AE113" s="48"/>
+      <c r="R113" s="50"/>
+      <c r="S113" s="51"/>
+      <c r="T113" s="50"/>
+      <c r="U113" s="51"/>
+      <c r="V113" s="50"/>
+      <c r="W113" s="51"/>
+      <c r="X113" s="43"/>
+      <c r="Y113" s="44"/>
+      <c r="Z113" s="43"/>
+      <c r="AA113" s="44"/>
+      <c r="AB113" s="43"/>
+      <c r="AC113" s="44"/>
+      <c r="AD113" s="43"/>
+      <c r="AE113" s="44"/>
       <c r="AF113" s="22"/>
       <c r="AG113" s="22"/>
       <c r="AH113" s="22"/>
@@ -5459,20 +5459,20 @@
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="3"/>
-      <c r="R114" s="49"/>
-      <c r="S114" s="50"/>
-      <c r="T114" s="49"/>
-      <c r="U114" s="50"/>
-      <c r="V114" s="49"/>
-      <c r="W114" s="50"/>
-      <c r="X114" s="47"/>
-      <c r="Y114" s="48"/>
-      <c r="Z114" s="47"/>
-      <c r="AA114" s="48"/>
-      <c r="AB114" s="47"/>
-      <c r="AC114" s="48"/>
-      <c r="AD114" s="47"/>
-      <c r="AE114" s="48"/>
+      <c r="R114" s="50"/>
+      <c r="S114" s="51"/>
+      <c r="T114" s="50"/>
+      <c r="U114" s="51"/>
+      <c r="V114" s="50"/>
+      <c r="W114" s="51"/>
+      <c r="X114" s="43"/>
+      <c r="Y114" s="44"/>
+      <c r="Z114" s="43"/>
+      <c r="AA114" s="44"/>
+      <c r="AB114" s="43"/>
+      <c r="AC114" s="44"/>
+      <c r="AD114" s="43"/>
+      <c r="AE114" s="44"/>
       <c r="AF114" s="1"/>
       <c r="AG114" s="1"/>
       <c r="AH114" s="22"/>
@@ -5496,20 +5496,20 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
       <c r="Q115" s="3"/>
-      <c r="R115" s="49"/>
-      <c r="S115" s="50"/>
-      <c r="T115" s="49"/>
-      <c r="U115" s="50"/>
-      <c r="V115" s="49"/>
-      <c r="W115" s="50"/>
-      <c r="X115" s="47"/>
-      <c r="Y115" s="48"/>
-      <c r="Z115" s="47"/>
-      <c r="AA115" s="48"/>
-      <c r="AB115" s="47"/>
-      <c r="AC115" s="48"/>
-      <c r="AD115" s="47"/>
-      <c r="AE115" s="48"/>
+      <c r="R115" s="50"/>
+      <c r="S115" s="51"/>
+      <c r="T115" s="50"/>
+      <c r="U115" s="51"/>
+      <c r="V115" s="50"/>
+      <c r="W115" s="51"/>
+      <c r="X115" s="43"/>
+      <c r="Y115" s="44"/>
+      <c r="Z115" s="43"/>
+      <c r="AA115" s="44"/>
+      <c r="AB115" s="43"/>
+      <c r="AC115" s="44"/>
+      <c r="AD115" s="43"/>
+      <c r="AE115" s="44"/>
       <c r="AF115" s="22"/>
       <c r="AG115" s="22"/>
       <c r="AH115" s="22"/>
@@ -5533,20 +5533,20 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
       <c r="Q116" s="3"/>
-      <c r="R116" s="49"/>
-      <c r="S116" s="50"/>
-      <c r="T116" s="49"/>
-      <c r="U116" s="50"/>
-      <c r="V116" s="49"/>
-      <c r="W116" s="50"/>
-      <c r="X116" s="47"/>
-      <c r="Y116" s="48"/>
-      <c r="Z116" s="47"/>
-      <c r="AA116" s="48"/>
-      <c r="AB116" s="47"/>
-      <c r="AC116" s="48"/>
-      <c r="AD116" s="47"/>
-      <c r="AE116" s="48"/>
+      <c r="R116" s="50"/>
+      <c r="S116" s="51"/>
+      <c r="T116" s="50"/>
+      <c r="U116" s="51"/>
+      <c r="V116" s="50"/>
+      <c r="W116" s="51"/>
+      <c r="X116" s="43"/>
+      <c r="Y116" s="44"/>
+      <c r="Z116" s="43"/>
+      <c r="AA116" s="44"/>
+      <c r="AB116" s="43"/>
+      <c r="AC116" s="44"/>
+      <c r="AD116" s="43"/>
+      <c r="AE116" s="44"/>
       <c r="AF116" s="22"/>
       <c r="AG116" s="22"/>
       <c r="AH116" s="22"/>
@@ -5570,20 +5570,20 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
       <c r="Q117" s="3"/>
-      <c r="R117" s="49"/>
-      <c r="S117" s="50"/>
-      <c r="T117" s="49"/>
-      <c r="U117" s="50"/>
-      <c r="V117" s="49"/>
-      <c r="W117" s="50"/>
-      <c r="X117" s="47"/>
-      <c r="Y117" s="48"/>
-      <c r="Z117" s="47"/>
-      <c r="AA117" s="48"/>
-      <c r="AB117" s="47"/>
-      <c r="AC117" s="48"/>
-      <c r="AD117" s="47"/>
-      <c r="AE117" s="48"/>
+      <c r="R117" s="50"/>
+      <c r="S117" s="51"/>
+      <c r="T117" s="50"/>
+      <c r="U117" s="51"/>
+      <c r="V117" s="50"/>
+      <c r="W117" s="51"/>
+      <c r="X117" s="43"/>
+      <c r="Y117" s="44"/>
+      <c r="Z117" s="43"/>
+      <c r="AA117" s="44"/>
+      <c r="AB117" s="43"/>
+      <c r="AC117" s="44"/>
+      <c r="AD117" s="43"/>
+      <c r="AE117" s="44"/>
       <c r="AF117" s="22"/>
       <c r="AG117" s="22"/>
       <c r="AH117" s="22"/>
@@ -5607,20 +5607,20 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
       <c r="Q118" s="3"/>
-      <c r="R118" s="49"/>
-      <c r="S118" s="50"/>
-      <c r="T118" s="49"/>
-      <c r="U118" s="50"/>
-      <c r="V118" s="49"/>
-      <c r="W118" s="50"/>
-      <c r="X118" s="47"/>
-      <c r="Y118" s="48"/>
-      <c r="Z118" s="47"/>
-      <c r="AA118" s="48"/>
-      <c r="AB118" s="47"/>
-      <c r="AC118" s="48"/>
-      <c r="AD118" s="47"/>
-      <c r="AE118" s="48"/>
+      <c r="R118" s="50"/>
+      <c r="S118" s="51"/>
+      <c r="T118" s="50"/>
+      <c r="U118" s="51"/>
+      <c r="V118" s="50"/>
+      <c r="W118" s="51"/>
+      <c r="X118" s="43"/>
+      <c r="Y118" s="44"/>
+      <c r="Z118" s="43"/>
+      <c r="AA118" s="44"/>
+      <c r="AB118" s="43"/>
+      <c r="AC118" s="44"/>
+      <c r="AD118" s="43"/>
+      <c r="AE118" s="44"/>
       <c r="AF118" s="22"/>
       <c r="AG118" s="22"/>
       <c r="AH118" s="22"/>
@@ -5644,20 +5644,20 @@
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="3"/>
-      <c r="R119" s="49"/>
-      <c r="S119" s="50"/>
-      <c r="T119" s="49"/>
-      <c r="U119" s="50"/>
-      <c r="V119" s="49"/>
-      <c r="W119" s="50"/>
-      <c r="X119" s="47"/>
-      <c r="Y119" s="48"/>
-      <c r="Z119" s="47"/>
-      <c r="AA119" s="48"/>
-      <c r="AB119" s="47"/>
-      <c r="AC119" s="48"/>
-      <c r="AD119" s="47"/>
-      <c r="AE119" s="48"/>
+      <c r="R119" s="50"/>
+      <c r="S119" s="51"/>
+      <c r="T119" s="50"/>
+      <c r="U119" s="51"/>
+      <c r="V119" s="50"/>
+      <c r="W119" s="51"/>
+      <c r="X119" s="43"/>
+      <c r="Y119" s="44"/>
+      <c r="Z119" s="43"/>
+      <c r="AA119" s="44"/>
+      <c r="AB119" s="43"/>
+      <c r="AC119" s="44"/>
+      <c r="AD119" s="43"/>
+      <c r="AE119" s="44"/>
       <c r="AF119" s="22"/>
       <c r="AG119" s="22"/>
       <c r="AH119" s="22"/>
@@ -5681,20 +5681,20 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="3"/>
-      <c r="R120" s="49"/>
-      <c r="S120" s="50"/>
-      <c r="T120" s="49"/>
-      <c r="U120" s="50"/>
-      <c r="V120" s="49"/>
-      <c r="W120" s="50"/>
-      <c r="X120" s="47"/>
-      <c r="Y120" s="48"/>
-      <c r="Z120" s="47"/>
-      <c r="AA120" s="48"/>
-      <c r="AB120" s="47"/>
-      <c r="AC120" s="48"/>
-      <c r="AD120" s="47"/>
-      <c r="AE120" s="48"/>
+      <c r="R120" s="50"/>
+      <c r="S120" s="51"/>
+      <c r="T120" s="50"/>
+      <c r="U120" s="51"/>
+      <c r="V120" s="50"/>
+      <c r="W120" s="51"/>
+      <c r="X120" s="43"/>
+      <c r="Y120" s="44"/>
+      <c r="Z120" s="43"/>
+      <c r="AA120" s="44"/>
+      <c r="AB120" s="43"/>
+      <c r="AC120" s="44"/>
+      <c r="AD120" s="43"/>
+      <c r="AE120" s="44"/>
       <c r="AF120" s="1"/>
       <c r="AG120" s="22"/>
       <c r="AH120" s="22"/>
@@ -5718,20 +5718,20 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="3"/>
-      <c r="R121" s="49"/>
-      <c r="S121" s="50"/>
-      <c r="T121" s="49"/>
-      <c r="U121" s="50"/>
-      <c r="V121" s="49"/>
-      <c r="W121" s="50"/>
-      <c r="X121" s="47"/>
-      <c r="Y121" s="48"/>
-      <c r="Z121" s="47"/>
-      <c r="AA121" s="48"/>
-      <c r="AB121" s="47"/>
-      <c r="AC121" s="48"/>
-      <c r="AD121" s="47"/>
-      <c r="AE121" s="48"/>
+      <c r="R121" s="50"/>
+      <c r="S121" s="51"/>
+      <c r="T121" s="50"/>
+      <c r="U121" s="51"/>
+      <c r="V121" s="50"/>
+      <c r="W121" s="51"/>
+      <c r="X121" s="43"/>
+      <c r="Y121" s="44"/>
+      <c r="Z121" s="43"/>
+      <c r="AA121" s="44"/>
+      <c r="AB121" s="43"/>
+      <c r="AC121" s="44"/>
+      <c r="AD121" s="43"/>
+      <c r="AE121" s="44"/>
       <c r="AF121" s="1"/>
       <c r="AG121" s="22"/>
       <c r="AH121" s="22"/>
@@ -5804,8 +5804,8 @@
       <c r="AA123" s="42"/>
       <c r="AB123" s="41"/>
       <c r="AC123" s="42"/>
-      <c r="AD123" s="47"/>
-      <c r="AE123" s="48"/>
+      <c r="AD123" s="43"/>
+      <c r="AE123" s="44"/>
       <c r="AF123" s="1"/>
       <c r="AG123" s="1"/>
       <c r="AH123" s="20"/>
@@ -5841,8 +5841,8 @@
       <c r="AA124" s="42"/>
       <c r="AB124" s="41"/>
       <c r="AC124" s="42"/>
-      <c r="AD124" s="47"/>
-      <c r="AE124" s="48"/>
+      <c r="AD124" s="43"/>
+      <c r="AE124" s="44"/>
       <c r="AF124" s="1"/>
       <c r="AG124" s="1"/>
       <c r="AH124" s="1"/>
@@ -7835,8 +7835,8 @@
       <c r="W178" s="42"/>
       <c r="X178" s="41"/>
       <c r="Y178" s="42"/>
-      <c r="Z178" s="47"/>
-      <c r="AA178" s="48"/>
+      <c r="Z178" s="43"/>
+      <c r="AA178" s="44"/>
       <c r="AB178" s="41"/>
       <c r="AC178" s="42"/>
       <c r="AD178" s="41"/>
@@ -8359,47 +8359,1200 @@
     <sortCondition ref="A11:A134"/>
   </sortState>
   <mergeCells count="1267">
-    <mergeCell ref="Z29:AA29"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="AB39:AC39"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="Z40:AA40"/>
-    <mergeCell ref="AB37:AC37"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="AI8:AI10"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="AH8:AH10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="Z35:AA35"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AB34:AC34"/>
-    <mergeCell ref="AB33:AC33"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="AB31:AC31"/>
-    <mergeCell ref="AB30:AC30"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="AB29:AC29"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="AB27:AC27"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="Z9:AA10"/>
+    <mergeCell ref="X9:Y10"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="T9:U10"/>
+    <mergeCell ref="AD14:AE14"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="AD9:AE10"/>
+    <mergeCell ref="AB9:AC10"/>
+    <mergeCell ref="R186:S186"/>
+    <mergeCell ref="T186:U186"/>
+    <mergeCell ref="V186:W186"/>
+    <mergeCell ref="X186:Y186"/>
+    <mergeCell ref="Z186:AA186"/>
+    <mergeCell ref="AB186:AC186"/>
+    <mergeCell ref="AD186:AE186"/>
+    <mergeCell ref="R184:S184"/>
+    <mergeCell ref="T184:U184"/>
+    <mergeCell ref="V184:W184"/>
+    <mergeCell ref="X184:Y184"/>
+    <mergeCell ref="Z184:AA184"/>
+    <mergeCell ref="AB184:AC184"/>
+    <mergeCell ref="AD184:AE184"/>
+    <mergeCell ref="R185:S185"/>
+    <mergeCell ref="T185:U185"/>
+    <mergeCell ref="V185:W185"/>
+    <mergeCell ref="X185:Y185"/>
+    <mergeCell ref="Z185:AA185"/>
+    <mergeCell ref="AB185:AC185"/>
+    <mergeCell ref="AD185:AE185"/>
+    <mergeCell ref="R183:S183"/>
+    <mergeCell ref="T183:U183"/>
+    <mergeCell ref="V183:W183"/>
+    <mergeCell ref="X183:Y183"/>
+    <mergeCell ref="Z183:AA183"/>
+    <mergeCell ref="AB183:AC183"/>
+    <mergeCell ref="AD183:AE183"/>
+    <mergeCell ref="R181:S181"/>
+    <mergeCell ref="T181:U181"/>
+    <mergeCell ref="V181:W181"/>
+    <mergeCell ref="X181:Y181"/>
+    <mergeCell ref="Z181:AA181"/>
+    <mergeCell ref="AB181:AC181"/>
+    <mergeCell ref="AD181:AE181"/>
+    <mergeCell ref="R182:S182"/>
+    <mergeCell ref="T182:U182"/>
+    <mergeCell ref="V182:W182"/>
+    <mergeCell ref="X182:Y182"/>
+    <mergeCell ref="Z182:AA182"/>
+    <mergeCell ref="AB182:AC182"/>
+    <mergeCell ref="AD182:AE182"/>
+    <mergeCell ref="R179:S179"/>
+    <mergeCell ref="T179:U179"/>
+    <mergeCell ref="V179:W179"/>
+    <mergeCell ref="X179:Y179"/>
+    <mergeCell ref="Z179:AA179"/>
+    <mergeCell ref="AB179:AC179"/>
+    <mergeCell ref="AD179:AE179"/>
+    <mergeCell ref="R180:S180"/>
+    <mergeCell ref="T180:U180"/>
+    <mergeCell ref="V180:W180"/>
+    <mergeCell ref="X180:Y180"/>
+    <mergeCell ref="Z180:AA180"/>
+    <mergeCell ref="AB180:AC180"/>
+    <mergeCell ref="AD180:AE180"/>
+    <mergeCell ref="R177:S177"/>
+    <mergeCell ref="T177:U177"/>
+    <mergeCell ref="V177:W177"/>
+    <mergeCell ref="X177:Y177"/>
+    <mergeCell ref="Z177:AA177"/>
+    <mergeCell ref="AB177:AC177"/>
+    <mergeCell ref="AD177:AE177"/>
+    <mergeCell ref="R178:S178"/>
+    <mergeCell ref="T178:U178"/>
+    <mergeCell ref="V178:W178"/>
+    <mergeCell ref="X178:Y178"/>
+    <mergeCell ref="Z178:AA178"/>
+    <mergeCell ref="AB178:AC178"/>
+    <mergeCell ref="AD178:AE178"/>
+    <mergeCell ref="R175:S175"/>
+    <mergeCell ref="T175:U175"/>
+    <mergeCell ref="V175:W175"/>
+    <mergeCell ref="X175:Y175"/>
+    <mergeCell ref="Z175:AA175"/>
+    <mergeCell ref="AB175:AC175"/>
+    <mergeCell ref="AD175:AE175"/>
+    <mergeCell ref="R176:S176"/>
+    <mergeCell ref="T176:U176"/>
+    <mergeCell ref="V176:W176"/>
+    <mergeCell ref="X176:Y176"/>
+    <mergeCell ref="Z176:AA176"/>
+    <mergeCell ref="AB176:AC176"/>
+    <mergeCell ref="AD176:AE176"/>
+    <mergeCell ref="R173:S173"/>
+    <mergeCell ref="T173:U173"/>
+    <mergeCell ref="V173:W173"/>
+    <mergeCell ref="X173:Y173"/>
+    <mergeCell ref="Z173:AA173"/>
+    <mergeCell ref="AB173:AC173"/>
+    <mergeCell ref="AD173:AE173"/>
+    <mergeCell ref="R174:S174"/>
+    <mergeCell ref="T174:U174"/>
+    <mergeCell ref="V174:W174"/>
+    <mergeCell ref="X174:Y174"/>
+    <mergeCell ref="Z174:AA174"/>
+    <mergeCell ref="AB174:AC174"/>
+    <mergeCell ref="AD174:AE174"/>
+    <mergeCell ref="R171:S171"/>
+    <mergeCell ref="T171:U171"/>
+    <mergeCell ref="V171:W171"/>
+    <mergeCell ref="X171:Y171"/>
+    <mergeCell ref="Z171:AA171"/>
+    <mergeCell ref="AB171:AC171"/>
+    <mergeCell ref="AD171:AE171"/>
+    <mergeCell ref="R172:S172"/>
+    <mergeCell ref="T172:U172"/>
+    <mergeCell ref="V172:W172"/>
+    <mergeCell ref="X172:Y172"/>
+    <mergeCell ref="Z172:AA172"/>
+    <mergeCell ref="AB172:AC172"/>
+    <mergeCell ref="AD172:AE172"/>
+    <mergeCell ref="R169:S169"/>
+    <mergeCell ref="T169:U169"/>
+    <mergeCell ref="V169:W169"/>
+    <mergeCell ref="X169:Y169"/>
+    <mergeCell ref="Z169:AA169"/>
+    <mergeCell ref="AB169:AC169"/>
+    <mergeCell ref="AD169:AE169"/>
+    <mergeCell ref="R170:S170"/>
+    <mergeCell ref="T170:U170"/>
+    <mergeCell ref="V170:W170"/>
+    <mergeCell ref="X170:Y170"/>
+    <mergeCell ref="Z170:AA170"/>
+    <mergeCell ref="AB170:AC170"/>
+    <mergeCell ref="AD170:AE170"/>
+    <mergeCell ref="R167:S167"/>
+    <mergeCell ref="T167:U167"/>
+    <mergeCell ref="V167:W167"/>
+    <mergeCell ref="X167:Y167"/>
+    <mergeCell ref="Z167:AA167"/>
+    <mergeCell ref="AB167:AC167"/>
+    <mergeCell ref="AD167:AE167"/>
+    <mergeCell ref="R168:S168"/>
+    <mergeCell ref="T168:U168"/>
+    <mergeCell ref="V168:W168"/>
+    <mergeCell ref="X168:Y168"/>
+    <mergeCell ref="Z168:AA168"/>
+    <mergeCell ref="AB168:AC168"/>
+    <mergeCell ref="AD168:AE168"/>
+    <mergeCell ref="R165:S165"/>
+    <mergeCell ref="T165:U165"/>
+    <mergeCell ref="V165:W165"/>
+    <mergeCell ref="X165:Y165"/>
+    <mergeCell ref="Z165:AA165"/>
+    <mergeCell ref="AB165:AC165"/>
+    <mergeCell ref="AD165:AE165"/>
+    <mergeCell ref="R166:S166"/>
+    <mergeCell ref="T166:U166"/>
+    <mergeCell ref="V166:W166"/>
+    <mergeCell ref="X166:Y166"/>
+    <mergeCell ref="Z166:AA166"/>
+    <mergeCell ref="AB166:AC166"/>
+    <mergeCell ref="AD166:AE166"/>
+    <mergeCell ref="R163:S163"/>
+    <mergeCell ref="T163:U163"/>
+    <mergeCell ref="V163:W163"/>
+    <mergeCell ref="X163:Y163"/>
+    <mergeCell ref="Z163:AA163"/>
+    <mergeCell ref="AB163:AC163"/>
+    <mergeCell ref="AD163:AE163"/>
+    <mergeCell ref="R164:S164"/>
+    <mergeCell ref="T164:U164"/>
+    <mergeCell ref="V164:W164"/>
+    <mergeCell ref="X164:Y164"/>
+    <mergeCell ref="Z164:AA164"/>
+    <mergeCell ref="AB164:AC164"/>
+    <mergeCell ref="AD164:AE164"/>
+    <mergeCell ref="R161:S161"/>
+    <mergeCell ref="T161:U161"/>
+    <mergeCell ref="V161:W161"/>
+    <mergeCell ref="X161:Y161"/>
+    <mergeCell ref="Z161:AA161"/>
+    <mergeCell ref="AB161:AC161"/>
+    <mergeCell ref="AD161:AE161"/>
+    <mergeCell ref="R162:S162"/>
+    <mergeCell ref="T162:U162"/>
+    <mergeCell ref="V162:W162"/>
+    <mergeCell ref="X162:Y162"/>
+    <mergeCell ref="Z162:AA162"/>
+    <mergeCell ref="AB162:AC162"/>
+    <mergeCell ref="AD162:AE162"/>
+    <mergeCell ref="R159:S159"/>
+    <mergeCell ref="T159:U159"/>
+    <mergeCell ref="V159:W159"/>
+    <mergeCell ref="X159:Y159"/>
+    <mergeCell ref="Z159:AA159"/>
+    <mergeCell ref="AB159:AC159"/>
+    <mergeCell ref="AD159:AE159"/>
+    <mergeCell ref="R160:S160"/>
+    <mergeCell ref="T160:U160"/>
+    <mergeCell ref="V160:W160"/>
+    <mergeCell ref="X160:Y160"/>
+    <mergeCell ref="Z160:AA160"/>
+    <mergeCell ref="AB160:AC160"/>
+    <mergeCell ref="AD160:AE160"/>
+    <mergeCell ref="R157:S157"/>
+    <mergeCell ref="T157:U157"/>
+    <mergeCell ref="V157:W157"/>
+    <mergeCell ref="X157:Y157"/>
+    <mergeCell ref="Z157:AA157"/>
+    <mergeCell ref="AB157:AC157"/>
+    <mergeCell ref="AD157:AE157"/>
+    <mergeCell ref="R158:S158"/>
+    <mergeCell ref="T158:U158"/>
+    <mergeCell ref="V158:W158"/>
+    <mergeCell ref="X158:Y158"/>
+    <mergeCell ref="Z158:AA158"/>
+    <mergeCell ref="AB158:AC158"/>
+    <mergeCell ref="AD158:AE158"/>
+    <mergeCell ref="R155:S155"/>
+    <mergeCell ref="T155:U155"/>
+    <mergeCell ref="V155:W155"/>
+    <mergeCell ref="X155:Y155"/>
+    <mergeCell ref="Z155:AA155"/>
+    <mergeCell ref="AB155:AC155"/>
+    <mergeCell ref="AD155:AE155"/>
+    <mergeCell ref="R156:S156"/>
+    <mergeCell ref="T156:U156"/>
+    <mergeCell ref="V156:W156"/>
+    <mergeCell ref="X156:Y156"/>
+    <mergeCell ref="Z156:AA156"/>
+    <mergeCell ref="AB156:AC156"/>
+    <mergeCell ref="AD156:AE156"/>
+    <mergeCell ref="R153:S153"/>
+    <mergeCell ref="T153:U153"/>
+    <mergeCell ref="V153:W153"/>
+    <mergeCell ref="X153:Y153"/>
+    <mergeCell ref="Z153:AA153"/>
+    <mergeCell ref="AB153:AC153"/>
+    <mergeCell ref="AD153:AE153"/>
+    <mergeCell ref="R154:S154"/>
+    <mergeCell ref="T154:U154"/>
+    <mergeCell ref="V154:W154"/>
+    <mergeCell ref="X154:Y154"/>
+    <mergeCell ref="Z154:AA154"/>
+    <mergeCell ref="AB154:AC154"/>
+    <mergeCell ref="AD154:AE154"/>
+    <mergeCell ref="R151:S151"/>
+    <mergeCell ref="T151:U151"/>
+    <mergeCell ref="V151:W151"/>
+    <mergeCell ref="X151:Y151"/>
+    <mergeCell ref="Z151:AA151"/>
+    <mergeCell ref="AB151:AC151"/>
+    <mergeCell ref="AD151:AE151"/>
+    <mergeCell ref="R152:S152"/>
+    <mergeCell ref="T152:U152"/>
+    <mergeCell ref="V152:W152"/>
+    <mergeCell ref="X152:Y152"/>
+    <mergeCell ref="Z152:AA152"/>
+    <mergeCell ref="AB152:AC152"/>
+    <mergeCell ref="AD152:AE152"/>
+    <mergeCell ref="R149:S149"/>
+    <mergeCell ref="T149:U149"/>
+    <mergeCell ref="V149:W149"/>
+    <mergeCell ref="X149:Y149"/>
+    <mergeCell ref="Z149:AA149"/>
+    <mergeCell ref="AB149:AC149"/>
+    <mergeCell ref="AD149:AE149"/>
+    <mergeCell ref="R150:S150"/>
+    <mergeCell ref="T150:U150"/>
+    <mergeCell ref="V150:W150"/>
+    <mergeCell ref="X150:Y150"/>
+    <mergeCell ref="Z150:AA150"/>
+    <mergeCell ref="AB150:AC150"/>
+    <mergeCell ref="AD150:AE150"/>
+    <mergeCell ref="R147:S147"/>
+    <mergeCell ref="T147:U147"/>
+    <mergeCell ref="V147:W147"/>
+    <mergeCell ref="X147:Y147"/>
+    <mergeCell ref="Z147:AA147"/>
+    <mergeCell ref="AB147:AC147"/>
+    <mergeCell ref="AD147:AE147"/>
+    <mergeCell ref="R148:S148"/>
+    <mergeCell ref="T148:U148"/>
+    <mergeCell ref="V148:W148"/>
+    <mergeCell ref="X148:Y148"/>
+    <mergeCell ref="Z148:AA148"/>
+    <mergeCell ref="AB148:AC148"/>
+    <mergeCell ref="AD148:AE148"/>
+    <mergeCell ref="R145:S145"/>
+    <mergeCell ref="T145:U145"/>
+    <mergeCell ref="V145:W145"/>
+    <mergeCell ref="X145:Y145"/>
+    <mergeCell ref="Z145:AA145"/>
+    <mergeCell ref="AB145:AC145"/>
+    <mergeCell ref="AD145:AE145"/>
+    <mergeCell ref="R146:S146"/>
+    <mergeCell ref="T146:U146"/>
+    <mergeCell ref="V146:W146"/>
+    <mergeCell ref="X146:Y146"/>
+    <mergeCell ref="Z146:AA146"/>
+    <mergeCell ref="AB146:AC146"/>
+    <mergeCell ref="AD146:AE146"/>
+    <mergeCell ref="R143:S143"/>
+    <mergeCell ref="T143:U143"/>
+    <mergeCell ref="V143:W143"/>
+    <mergeCell ref="X143:Y143"/>
+    <mergeCell ref="Z143:AA143"/>
+    <mergeCell ref="AB143:AC143"/>
+    <mergeCell ref="AD143:AE143"/>
+    <mergeCell ref="R144:S144"/>
+    <mergeCell ref="T144:U144"/>
+    <mergeCell ref="V144:W144"/>
+    <mergeCell ref="X144:Y144"/>
+    <mergeCell ref="Z144:AA144"/>
+    <mergeCell ref="AB144:AC144"/>
+    <mergeCell ref="AD144:AE144"/>
+    <mergeCell ref="R141:S141"/>
+    <mergeCell ref="T141:U141"/>
+    <mergeCell ref="V141:W141"/>
+    <mergeCell ref="X141:Y141"/>
+    <mergeCell ref="Z141:AA141"/>
+    <mergeCell ref="AB141:AC141"/>
+    <mergeCell ref="AD141:AE141"/>
+    <mergeCell ref="R142:S142"/>
+    <mergeCell ref="T142:U142"/>
+    <mergeCell ref="V142:W142"/>
+    <mergeCell ref="X142:Y142"/>
+    <mergeCell ref="Z142:AA142"/>
+    <mergeCell ref="AB142:AC142"/>
+    <mergeCell ref="AD142:AE142"/>
+    <mergeCell ref="R139:S139"/>
+    <mergeCell ref="T139:U139"/>
+    <mergeCell ref="V139:W139"/>
+    <mergeCell ref="X139:Y139"/>
+    <mergeCell ref="Z139:AA139"/>
+    <mergeCell ref="AB139:AC139"/>
+    <mergeCell ref="AD139:AE139"/>
+    <mergeCell ref="R140:S140"/>
+    <mergeCell ref="T140:U140"/>
+    <mergeCell ref="V140:W140"/>
+    <mergeCell ref="X140:Y140"/>
+    <mergeCell ref="Z140:AA140"/>
+    <mergeCell ref="AB140:AC140"/>
+    <mergeCell ref="AD140:AE140"/>
+    <mergeCell ref="R137:S137"/>
+    <mergeCell ref="T137:U137"/>
+    <mergeCell ref="V137:W137"/>
+    <mergeCell ref="X137:Y137"/>
+    <mergeCell ref="Z137:AA137"/>
+    <mergeCell ref="AB137:AC137"/>
+    <mergeCell ref="AD137:AE137"/>
+    <mergeCell ref="R138:S138"/>
+    <mergeCell ref="T138:U138"/>
+    <mergeCell ref="V138:W138"/>
+    <mergeCell ref="X138:Y138"/>
+    <mergeCell ref="Z138:AA138"/>
+    <mergeCell ref="AB138:AC138"/>
+    <mergeCell ref="AD138:AE138"/>
+    <mergeCell ref="R135:S135"/>
+    <mergeCell ref="T135:U135"/>
+    <mergeCell ref="V135:W135"/>
+    <mergeCell ref="X135:Y135"/>
+    <mergeCell ref="Z135:AA135"/>
+    <mergeCell ref="AB135:AC135"/>
+    <mergeCell ref="AD135:AE135"/>
+    <mergeCell ref="R136:S136"/>
+    <mergeCell ref="T136:U136"/>
+    <mergeCell ref="V136:W136"/>
+    <mergeCell ref="X136:Y136"/>
+    <mergeCell ref="Z136:AA136"/>
+    <mergeCell ref="AB136:AC136"/>
+    <mergeCell ref="AD136:AE136"/>
+    <mergeCell ref="R133:S133"/>
+    <mergeCell ref="T133:U133"/>
+    <mergeCell ref="V133:W133"/>
+    <mergeCell ref="X133:Y133"/>
+    <mergeCell ref="Z133:AA133"/>
+    <mergeCell ref="AB133:AC133"/>
+    <mergeCell ref="AD133:AE133"/>
+    <mergeCell ref="R134:S134"/>
+    <mergeCell ref="T134:U134"/>
+    <mergeCell ref="V134:W134"/>
+    <mergeCell ref="X134:Y134"/>
+    <mergeCell ref="Z134:AA134"/>
+    <mergeCell ref="AB134:AC134"/>
+    <mergeCell ref="AD134:AE134"/>
+    <mergeCell ref="R131:S131"/>
+    <mergeCell ref="T131:U131"/>
+    <mergeCell ref="V131:W131"/>
+    <mergeCell ref="X131:Y131"/>
+    <mergeCell ref="Z131:AA131"/>
+    <mergeCell ref="AB131:AC131"/>
+    <mergeCell ref="AD131:AE131"/>
+    <mergeCell ref="R132:S132"/>
+    <mergeCell ref="T132:U132"/>
+    <mergeCell ref="V132:W132"/>
+    <mergeCell ref="X132:Y132"/>
+    <mergeCell ref="Z132:AA132"/>
+    <mergeCell ref="AB132:AC132"/>
+    <mergeCell ref="AD132:AE132"/>
+    <mergeCell ref="R129:S129"/>
+    <mergeCell ref="T129:U129"/>
+    <mergeCell ref="V129:W129"/>
+    <mergeCell ref="X129:Y129"/>
+    <mergeCell ref="Z129:AA129"/>
+    <mergeCell ref="AB129:AC129"/>
+    <mergeCell ref="AD129:AE129"/>
+    <mergeCell ref="R130:S130"/>
+    <mergeCell ref="T130:U130"/>
+    <mergeCell ref="V130:W130"/>
+    <mergeCell ref="X130:Y130"/>
+    <mergeCell ref="Z130:AA130"/>
+    <mergeCell ref="AB130:AC130"/>
+    <mergeCell ref="AD130:AE130"/>
+    <mergeCell ref="R127:S127"/>
+    <mergeCell ref="T127:U127"/>
+    <mergeCell ref="V127:W127"/>
+    <mergeCell ref="X127:Y127"/>
+    <mergeCell ref="Z127:AA127"/>
+    <mergeCell ref="AB127:AC127"/>
+    <mergeCell ref="AD127:AE127"/>
+    <mergeCell ref="R128:S128"/>
+    <mergeCell ref="T128:U128"/>
+    <mergeCell ref="V128:W128"/>
+    <mergeCell ref="X128:Y128"/>
+    <mergeCell ref="Z128:AA128"/>
+    <mergeCell ref="AB128:AC128"/>
+    <mergeCell ref="AD128:AE128"/>
+    <mergeCell ref="R125:S125"/>
+    <mergeCell ref="T125:U125"/>
+    <mergeCell ref="V125:W125"/>
+    <mergeCell ref="X125:Y125"/>
+    <mergeCell ref="Z125:AA125"/>
+    <mergeCell ref="AB125:AC125"/>
+    <mergeCell ref="AD125:AE125"/>
+    <mergeCell ref="R126:S126"/>
+    <mergeCell ref="T126:U126"/>
+    <mergeCell ref="V126:W126"/>
+    <mergeCell ref="X126:Y126"/>
+    <mergeCell ref="Z126:AA126"/>
+    <mergeCell ref="AB126:AC126"/>
+    <mergeCell ref="AD126:AE126"/>
+    <mergeCell ref="R123:S123"/>
+    <mergeCell ref="T123:U123"/>
+    <mergeCell ref="V123:W123"/>
+    <mergeCell ref="X123:Y123"/>
+    <mergeCell ref="Z123:AA123"/>
+    <mergeCell ref="AB123:AC123"/>
+    <mergeCell ref="AD123:AE123"/>
+    <mergeCell ref="R124:S124"/>
+    <mergeCell ref="T124:U124"/>
+    <mergeCell ref="V124:W124"/>
+    <mergeCell ref="X124:Y124"/>
+    <mergeCell ref="Z124:AA124"/>
+    <mergeCell ref="AB124:AC124"/>
+    <mergeCell ref="AD124:AE124"/>
+    <mergeCell ref="R121:S121"/>
+    <mergeCell ref="T121:U121"/>
+    <mergeCell ref="V121:W121"/>
+    <mergeCell ref="X121:Y121"/>
+    <mergeCell ref="Z121:AA121"/>
+    <mergeCell ref="AB121:AC121"/>
+    <mergeCell ref="AD121:AE121"/>
+    <mergeCell ref="R122:S122"/>
+    <mergeCell ref="T122:U122"/>
+    <mergeCell ref="V122:W122"/>
+    <mergeCell ref="X122:Y122"/>
+    <mergeCell ref="Z122:AA122"/>
+    <mergeCell ref="AB122:AC122"/>
+    <mergeCell ref="AD122:AE122"/>
+    <mergeCell ref="R119:S119"/>
+    <mergeCell ref="T119:U119"/>
+    <mergeCell ref="V119:W119"/>
+    <mergeCell ref="X119:Y119"/>
+    <mergeCell ref="Z119:AA119"/>
+    <mergeCell ref="AB119:AC119"/>
+    <mergeCell ref="AD119:AE119"/>
+    <mergeCell ref="R120:S120"/>
+    <mergeCell ref="T120:U120"/>
+    <mergeCell ref="V120:W120"/>
+    <mergeCell ref="X120:Y120"/>
+    <mergeCell ref="Z120:AA120"/>
+    <mergeCell ref="AB120:AC120"/>
+    <mergeCell ref="AD120:AE120"/>
+    <mergeCell ref="R117:S117"/>
+    <mergeCell ref="T117:U117"/>
+    <mergeCell ref="V117:W117"/>
+    <mergeCell ref="X117:Y117"/>
+    <mergeCell ref="Z117:AA117"/>
+    <mergeCell ref="AB117:AC117"/>
+    <mergeCell ref="AD117:AE117"/>
+    <mergeCell ref="R118:S118"/>
+    <mergeCell ref="T118:U118"/>
+    <mergeCell ref="V118:W118"/>
+    <mergeCell ref="X118:Y118"/>
+    <mergeCell ref="Z118:AA118"/>
+    <mergeCell ref="AB118:AC118"/>
+    <mergeCell ref="AD118:AE118"/>
+    <mergeCell ref="R115:S115"/>
+    <mergeCell ref="T115:U115"/>
+    <mergeCell ref="V115:W115"/>
+    <mergeCell ref="X115:Y115"/>
+    <mergeCell ref="Z115:AA115"/>
+    <mergeCell ref="AB115:AC115"/>
+    <mergeCell ref="AD115:AE115"/>
+    <mergeCell ref="R116:S116"/>
+    <mergeCell ref="T116:U116"/>
+    <mergeCell ref="V116:W116"/>
+    <mergeCell ref="X116:Y116"/>
+    <mergeCell ref="Z116:AA116"/>
+    <mergeCell ref="AB116:AC116"/>
+    <mergeCell ref="AD116:AE116"/>
+    <mergeCell ref="R113:S113"/>
+    <mergeCell ref="T113:U113"/>
+    <mergeCell ref="V113:W113"/>
+    <mergeCell ref="X113:Y113"/>
+    <mergeCell ref="Z113:AA113"/>
+    <mergeCell ref="AB113:AC113"/>
+    <mergeCell ref="AD113:AE113"/>
+    <mergeCell ref="R114:S114"/>
+    <mergeCell ref="T114:U114"/>
+    <mergeCell ref="V114:W114"/>
+    <mergeCell ref="X114:Y114"/>
+    <mergeCell ref="Z114:AA114"/>
+    <mergeCell ref="AB114:AC114"/>
+    <mergeCell ref="AD114:AE114"/>
+    <mergeCell ref="R111:S111"/>
+    <mergeCell ref="T111:U111"/>
+    <mergeCell ref="V111:W111"/>
+    <mergeCell ref="X111:Y111"/>
+    <mergeCell ref="Z111:AA111"/>
+    <mergeCell ref="AB111:AC111"/>
+    <mergeCell ref="AD111:AE111"/>
+    <mergeCell ref="R112:S112"/>
+    <mergeCell ref="T112:U112"/>
+    <mergeCell ref="V112:W112"/>
+    <mergeCell ref="X112:Y112"/>
+    <mergeCell ref="Z112:AA112"/>
+    <mergeCell ref="AB112:AC112"/>
+    <mergeCell ref="AD112:AE112"/>
+    <mergeCell ref="R109:S109"/>
+    <mergeCell ref="T109:U109"/>
+    <mergeCell ref="V109:W109"/>
+    <mergeCell ref="X109:Y109"/>
+    <mergeCell ref="Z109:AA109"/>
+    <mergeCell ref="AB109:AC109"/>
+    <mergeCell ref="AD109:AE109"/>
+    <mergeCell ref="R110:S110"/>
+    <mergeCell ref="T110:U110"/>
+    <mergeCell ref="V110:W110"/>
+    <mergeCell ref="X110:Y110"/>
+    <mergeCell ref="Z110:AA110"/>
+    <mergeCell ref="AB110:AC110"/>
+    <mergeCell ref="AD110:AE110"/>
+    <mergeCell ref="R107:S107"/>
+    <mergeCell ref="T107:U107"/>
+    <mergeCell ref="V107:W107"/>
+    <mergeCell ref="X107:Y107"/>
+    <mergeCell ref="Z107:AA107"/>
+    <mergeCell ref="AB107:AC107"/>
+    <mergeCell ref="AD107:AE107"/>
+    <mergeCell ref="R108:S108"/>
+    <mergeCell ref="T108:U108"/>
+    <mergeCell ref="V108:W108"/>
+    <mergeCell ref="X108:Y108"/>
+    <mergeCell ref="Z108:AA108"/>
+    <mergeCell ref="AB108:AC108"/>
+    <mergeCell ref="AD108:AE108"/>
+    <mergeCell ref="R105:S105"/>
+    <mergeCell ref="T105:U105"/>
+    <mergeCell ref="V105:W105"/>
+    <mergeCell ref="X105:Y105"/>
+    <mergeCell ref="Z105:AA105"/>
+    <mergeCell ref="AB105:AC105"/>
+    <mergeCell ref="AD105:AE105"/>
+    <mergeCell ref="R106:S106"/>
+    <mergeCell ref="T106:U106"/>
+    <mergeCell ref="V106:W106"/>
+    <mergeCell ref="X106:Y106"/>
+    <mergeCell ref="Z106:AA106"/>
+    <mergeCell ref="AB106:AC106"/>
+    <mergeCell ref="AD106:AE106"/>
+    <mergeCell ref="R103:S103"/>
+    <mergeCell ref="T103:U103"/>
+    <mergeCell ref="V103:W103"/>
+    <mergeCell ref="X103:Y103"/>
+    <mergeCell ref="Z103:AA103"/>
+    <mergeCell ref="AB103:AC103"/>
+    <mergeCell ref="AD103:AE103"/>
+    <mergeCell ref="R104:S104"/>
+    <mergeCell ref="T104:U104"/>
+    <mergeCell ref="V104:W104"/>
+    <mergeCell ref="X104:Y104"/>
+    <mergeCell ref="Z104:AA104"/>
+    <mergeCell ref="AB104:AC104"/>
+    <mergeCell ref="AD104:AE104"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="T101:U101"/>
+    <mergeCell ref="V101:W101"/>
+    <mergeCell ref="X101:Y101"/>
+    <mergeCell ref="Z101:AA101"/>
+    <mergeCell ref="AB101:AC101"/>
+    <mergeCell ref="AD101:AE101"/>
+    <mergeCell ref="R102:S102"/>
+    <mergeCell ref="T102:U102"/>
+    <mergeCell ref="V102:W102"/>
+    <mergeCell ref="X102:Y102"/>
+    <mergeCell ref="Z102:AA102"/>
+    <mergeCell ref="AB102:AC102"/>
+    <mergeCell ref="AD102:AE102"/>
+    <mergeCell ref="R99:S99"/>
+    <mergeCell ref="T99:U99"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="X99:Y99"/>
+    <mergeCell ref="Z99:AA99"/>
+    <mergeCell ref="AB99:AC99"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="R100:S100"/>
+    <mergeCell ref="T100:U100"/>
+    <mergeCell ref="V100:W100"/>
+    <mergeCell ref="X100:Y100"/>
+    <mergeCell ref="Z100:AA100"/>
+    <mergeCell ref="AB100:AC100"/>
+    <mergeCell ref="AD100:AE100"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="T97:U97"/>
+    <mergeCell ref="V97:W97"/>
+    <mergeCell ref="X97:Y97"/>
+    <mergeCell ref="Z97:AA97"/>
+    <mergeCell ref="AB97:AC97"/>
+    <mergeCell ref="AD97:AE97"/>
+    <mergeCell ref="R98:S98"/>
+    <mergeCell ref="T98:U98"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="X98:Y98"/>
+    <mergeCell ref="Z98:AA98"/>
+    <mergeCell ref="AB98:AC98"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="R95:S95"/>
+    <mergeCell ref="T95:U95"/>
+    <mergeCell ref="V95:W95"/>
+    <mergeCell ref="X95:Y95"/>
+    <mergeCell ref="Z95:AA95"/>
+    <mergeCell ref="AB95:AC95"/>
+    <mergeCell ref="AD95:AE95"/>
+    <mergeCell ref="R96:S96"/>
+    <mergeCell ref="T96:U96"/>
+    <mergeCell ref="V96:W96"/>
+    <mergeCell ref="X96:Y96"/>
+    <mergeCell ref="Z96:AA96"/>
+    <mergeCell ref="AB96:AC96"/>
+    <mergeCell ref="AD96:AE96"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="T93:U93"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="X93:Y93"/>
+    <mergeCell ref="Z93:AA93"/>
+    <mergeCell ref="AB93:AC93"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="R94:S94"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="V94:W94"/>
+    <mergeCell ref="X94:Y94"/>
+    <mergeCell ref="Z94:AA94"/>
+    <mergeCell ref="AB94:AC94"/>
+    <mergeCell ref="AD94:AE94"/>
+    <mergeCell ref="R91:S91"/>
+    <mergeCell ref="T91:U91"/>
+    <mergeCell ref="V91:W91"/>
+    <mergeCell ref="X91:Y91"/>
+    <mergeCell ref="Z91:AA91"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AD91:AE91"/>
+    <mergeCell ref="R92:S92"/>
+    <mergeCell ref="T92:U92"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="X92:Y92"/>
+    <mergeCell ref="Z92:AA92"/>
+    <mergeCell ref="AB92:AC92"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="T89:U89"/>
+    <mergeCell ref="V89:W89"/>
+    <mergeCell ref="X89:Y89"/>
+    <mergeCell ref="Z89:AA89"/>
+    <mergeCell ref="AB89:AC89"/>
+    <mergeCell ref="AD89:AE89"/>
+    <mergeCell ref="R90:S90"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="V90:W90"/>
+    <mergeCell ref="X90:Y90"/>
+    <mergeCell ref="Z90:AA90"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AD90:AE90"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="T87:U87"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="X87:Y87"/>
+    <mergeCell ref="Z87:AA87"/>
+    <mergeCell ref="AB87:AC87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="R88:S88"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="V88:W88"/>
+    <mergeCell ref="X88:Y88"/>
+    <mergeCell ref="Z88:AA88"/>
+    <mergeCell ref="AB88:AC88"/>
+    <mergeCell ref="AD88:AE88"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="T85:U85"/>
+    <mergeCell ref="V85:W85"/>
+    <mergeCell ref="X85:Y85"/>
+    <mergeCell ref="Z85:AA85"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AD85:AE85"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="T86:U86"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="X86:Y86"/>
+    <mergeCell ref="Z86:AA86"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="T83:U83"/>
+    <mergeCell ref="V83:W83"/>
+    <mergeCell ref="X83:Y83"/>
+    <mergeCell ref="Z83:AA83"/>
+    <mergeCell ref="AB83:AC83"/>
+    <mergeCell ref="AD83:AE83"/>
+    <mergeCell ref="R84:S84"/>
+    <mergeCell ref="T84:U84"/>
+    <mergeCell ref="V84:W84"/>
+    <mergeCell ref="X84:Y84"/>
+    <mergeCell ref="Z84:AA84"/>
+    <mergeCell ref="AB84:AC84"/>
+    <mergeCell ref="AD84:AE84"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="T81:U81"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="X81:Y81"/>
+    <mergeCell ref="Z81:AA81"/>
+    <mergeCell ref="AB81:AC81"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="R82:S82"/>
+    <mergeCell ref="T82:U82"/>
+    <mergeCell ref="V82:W82"/>
+    <mergeCell ref="X82:Y82"/>
+    <mergeCell ref="Z82:AA82"/>
+    <mergeCell ref="AB82:AC82"/>
+    <mergeCell ref="AD82:AE82"/>
+    <mergeCell ref="R79:S79"/>
+    <mergeCell ref="T79:U79"/>
+    <mergeCell ref="V79:W79"/>
+    <mergeCell ref="X79:Y79"/>
+    <mergeCell ref="Z79:AA79"/>
+    <mergeCell ref="AB79:AC79"/>
+    <mergeCell ref="AD79:AE79"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="T80:U80"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="X80:Y80"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="AB80:AC80"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="R77:S77"/>
+    <mergeCell ref="T77:U77"/>
+    <mergeCell ref="V77:W77"/>
+    <mergeCell ref="X77:Y77"/>
+    <mergeCell ref="Z77:AA77"/>
+    <mergeCell ref="AB77:AC77"/>
+    <mergeCell ref="AD77:AE77"/>
+    <mergeCell ref="R78:S78"/>
+    <mergeCell ref="T78:U78"/>
+    <mergeCell ref="V78:W78"/>
+    <mergeCell ref="X78:Y78"/>
+    <mergeCell ref="Z78:AA78"/>
+    <mergeCell ref="AB78:AC78"/>
+    <mergeCell ref="AD78:AE78"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="X75:Y75"/>
+    <mergeCell ref="Z75:AA75"/>
+    <mergeCell ref="AB75:AC75"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="V76:W76"/>
+    <mergeCell ref="X76:Y76"/>
+    <mergeCell ref="Z76:AA76"/>
+    <mergeCell ref="AB76:AC76"/>
+    <mergeCell ref="AD76:AE76"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="V73:W73"/>
+    <mergeCell ref="X73:Y73"/>
+    <mergeCell ref="Z73:AA73"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AD73:AE73"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="T74:U74"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="X74:Y74"/>
+    <mergeCell ref="Z74:AA74"/>
+    <mergeCell ref="AB74:AC74"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="T71:U71"/>
+    <mergeCell ref="V71:W71"/>
+    <mergeCell ref="X71:Y71"/>
+    <mergeCell ref="Z71:AA71"/>
+    <mergeCell ref="AB71:AC71"/>
+    <mergeCell ref="AD71:AE71"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T72:U72"/>
+    <mergeCell ref="V72:W72"/>
+    <mergeCell ref="X72:Y72"/>
+    <mergeCell ref="Z72:AA72"/>
+    <mergeCell ref="AB72:AC72"/>
+    <mergeCell ref="AD72:AE72"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="V69:W69"/>
+    <mergeCell ref="X69:Y69"/>
+    <mergeCell ref="Z69:AA69"/>
+    <mergeCell ref="AB69:AC69"/>
+    <mergeCell ref="AD69:AE69"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="V70:W70"/>
+    <mergeCell ref="X70:Y70"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AD70:AE70"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="V67:W67"/>
+    <mergeCell ref="X67:Y67"/>
+    <mergeCell ref="Z67:AA67"/>
+    <mergeCell ref="AB67:AC67"/>
+    <mergeCell ref="AD67:AE67"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="X68:Y68"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="AB68:AC68"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="T65:U65"/>
+    <mergeCell ref="V65:W65"/>
+    <mergeCell ref="X65:Y65"/>
+    <mergeCell ref="Z65:AA65"/>
+    <mergeCell ref="AB65:AC65"/>
+    <mergeCell ref="AD65:AE65"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="T66:U66"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="X66:Y66"/>
+    <mergeCell ref="Z66:AA66"/>
+    <mergeCell ref="AB66:AC66"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="T63:U63"/>
+    <mergeCell ref="V63:W63"/>
+    <mergeCell ref="X63:Y63"/>
+    <mergeCell ref="Z63:AA63"/>
+    <mergeCell ref="AB63:AC63"/>
+    <mergeCell ref="AD63:AE63"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="T64:U64"/>
+    <mergeCell ref="V64:W64"/>
+    <mergeCell ref="X64:Y64"/>
+    <mergeCell ref="Z64:AA64"/>
+    <mergeCell ref="AB64:AC64"/>
+    <mergeCell ref="AD64:AE64"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="V61:W61"/>
+    <mergeCell ref="X61:Y61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="AB61:AC61"/>
+    <mergeCell ref="AD61:AE61"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="V62:W62"/>
+    <mergeCell ref="X62:Y62"/>
+    <mergeCell ref="Z62:AA62"/>
+    <mergeCell ref="AB62:AC62"/>
+    <mergeCell ref="AD62:AE62"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="Z59:AA59"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="AB60:AC60"/>
+    <mergeCell ref="AD60:AE60"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="T57:U57"/>
+    <mergeCell ref="V57:W57"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AA57"/>
+    <mergeCell ref="AB57:AC57"/>
+    <mergeCell ref="AD57:AE57"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="Z58:AA58"/>
+    <mergeCell ref="AB58:AC58"/>
+    <mergeCell ref="AD58:AE58"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="V55:W55"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="Z55:AA55"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="AD55:AE55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="T56:U56"/>
+    <mergeCell ref="V56:W56"/>
+    <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="Z56:AA56"/>
+    <mergeCell ref="AB56:AC56"/>
+    <mergeCell ref="AD56:AE56"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="X53:Y53"/>
+    <mergeCell ref="Z53:AA53"/>
+    <mergeCell ref="AB53:AC53"/>
+    <mergeCell ref="AD53:AE53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="V54:W54"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="Z54:AA54"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="AD54:AE54"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="X51:Y51"/>
+    <mergeCell ref="Z51:AA51"/>
+    <mergeCell ref="AB51:AC51"/>
+    <mergeCell ref="AD51:AE51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="AB52:AC52"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="AB49:AC49"/>
+    <mergeCell ref="AD49:AE49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="Z50:AA50"/>
+    <mergeCell ref="AB50:AC50"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="V47:W47"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="Z47:AA47"/>
+    <mergeCell ref="AB47:AC47"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="Z48:AA48"/>
+    <mergeCell ref="AB48:AC48"/>
+    <mergeCell ref="AD48:AE48"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="Z45:AA45"/>
+    <mergeCell ref="AB45:AC45"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="V46:W46"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="Z46:AA46"/>
+    <mergeCell ref="AB46:AC46"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="AB43:AC43"/>
+    <mergeCell ref="AD43:AE43"/>
+    <mergeCell ref="T44:U44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="Z44:AA44"/>
+    <mergeCell ref="AB44:AC44"/>
+    <mergeCell ref="AD44:AE44"/>
+    <mergeCell ref="T41:U41"/>
+    <mergeCell ref="V41:W41"/>
+    <mergeCell ref="X41:Y41"/>
+    <mergeCell ref="Z41:AA41"/>
+    <mergeCell ref="AB41:AC41"/>
+    <mergeCell ref="AD41:AE41"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="V42:W42"/>
+    <mergeCell ref="X42:Y42"/>
+    <mergeCell ref="Z42:AA42"/>
+    <mergeCell ref="AB42:AC42"/>
+    <mergeCell ref="AD42:AE42"/>
+    <mergeCell ref="AF7:AH7"/>
+    <mergeCell ref="AG8:AG10"/>
+    <mergeCell ref="R1:V2"/>
+    <mergeCell ref="R4:V5"/>
+    <mergeCell ref="D3:Q3"/>
+    <mergeCell ref="D5:Q5"/>
+    <mergeCell ref="D4:Q4"/>
+    <mergeCell ref="R7:AE8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D1:Q1"/>
+    <mergeCell ref="D2:Q2"/>
+    <mergeCell ref="D6:Q6"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="A1:C6"/>
+    <mergeCell ref="A7:Q8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R9:S10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AD16:AE16"/>
+    <mergeCell ref="AB16:AC16"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="AB17:AC17"/>
+    <mergeCell ref="Z17:AA17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="AB22:AC22"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB24:AC24"/>
+    <mergeCell ref="AB25:AC25"/>
+    <mergeCell ref="AB26:AC26"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="AB11:AC11"/>
+    <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="AB21:AC21"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="AB18:AC18"/>
+    <mergeCell ref="Z18:AA18"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AB13:AC13"/>
+    <mergeCell ref="AB12:AC12"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="Z15:AA15"/>
+    <mergeCell ref="Z14:AA14"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AB14:AC14"/>
+    <mergeCell ref="AB15:AC15"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AB19:AC19"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="AD18:AE18"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="V39:W39"/>
+    <mergeCell ref="V40:W40"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="T19:U19"/>
@@ -8432,1200 +9585,47 @@
     <mergeCell ref="T23:U23"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="V22:W22"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="V39:W39"/>
-    <mergeCell ref="V40:W40"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="AD11:AE11"/>
-    <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="Z11:AA11"/>
-    <mergeCell ref="AD15:AE15"/>
-    <mergeCell ref="AB21:AC21"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="AB18:AC18"/>
-    <mergeCell ref="Z18:AA18"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AB13:AC13"/>
-    <mergeCell ref="AB12:AC12"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Z15:AA15"/>
-    <mergeCell ref="Z14:AA14"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AB14:AC14"/>
-    <mergeCell ref="AB15:AC15"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="AB16:AC16"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="AB17:AC17"/>
-    <mergeCell ref="Z17:AA17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="AB22:AC22"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC24"/>
-    <mergeCell ref="AB25:AC25"/>
-    <mergeCell ref="AB26:AC26"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R9:S10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="AF7:AH7"/>
-    <mergeCell ref="AG8:AG10"/>
-    <mergeCell ref="R1:V2"/>
-    <mergeCell ref="R4:V5"/>
-    <mergeCell ref="D3:Q3"/>
-    <mergeCell ref="D5:Q5"/>
-    <mergeCell ref="D4:Q4"/>
-    <mergeCell ref="R7:AE8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D1:Q1"/>
-    <mergeCell ref="D2:Q2"/>
-    <mergeCell ref="D6:Q6"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="A1:C6"/>
-    <mergeCell ref="A7:Q8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="AB43:AC43"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="T44:U44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="Z44:AA44"/>
-    <mergeCell ref="AB44:AC44"/>
-    <mergeCell ref="AD44:AE44"/>
-    <mergeCell ref="T41:U41"/>
-    <mergeCell ref="V41:W41"/>
-    <mergeCell ref="X41:Y41"/>
-    <mergeCell ref="Z41:AA41"/>
-    <mergeCell ref="AB41:AC41"/>
-    <mergeCell ref="AD41:AE41"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="V42:W42"/>
-    <mergeCell ref="X42:Y42"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AB42:AC42"/>
-    <mergeCell ref="AD42:AE42"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="V47:W47"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="Z47:AA47"/>
-    <mergeCell ref="AB47:AC47"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="V48:W48"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="Z48:AA48"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="AD48:AE48"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="AB45:AC45"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="V46:W46"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="Z46:AA46"/>
-    <mergeCell ref="AB46:AC46"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="X51:Y51"/>
-    <mergeCell ref="Z51:AA51"/>
-    <mergeCell ref="AB51:AC51"/>
-    <mergeCell ref="AD51:AE51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="V49:W49"/>
-    <mergeCell ref="X49:Y49"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="AB49:AC49"/>
-    <mergeCell ref="AD49:AE49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="V50:W50"/>
-    <mergeCell ref="X50:Y50"/>
-    <mergeCell ref="Z50:AA50"/>
-    <mergeCell ref="AB50:AC50"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="V55:W55"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="Z55:AA55"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="T56:U56"/>
-    <mergeCell ref="V56:W56"/>
-    <mergeCell ref="X56:Y56"/>
-    <mergeCell ref="Z56:AA56"/>
-    <mergeCell ref="AB56:AC56"/>
-    <mergeCell ref="AD56:AE56"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="X53:Y53"/>
-    <mergeCell ref="Z53:AA53"/>
-    <mergeCell ref="AB53:AC53"/>
-    <mergeCell ref="AD53:AE53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="V54:W54"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="Z54:AA54"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AD54:AE54"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="T59:U59"/>
-    <mergeCell ref="V59:W59"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="Z59:AA59"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="V60:W60"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="AB60:AC60"/>
-    <mergeCell ref="AD60:AE60"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="T57:U57"/>
-    <mergeCell ref="V57:W57"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AA57"/>
-    <mergeCell ref="AB57:AC57"/>
-    <mergeCell ref="AD57:AE57"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="V58:W58"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="Z58:AA58"/>
-    <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="AD58:AE58"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="V63:W63"/>
-    <mergeCell ref="X63:Y63"/>
-    <mergeCell ref="Z63:AA63"/>
-    <mergeCell ref="AB63:AC63"/>
-    <mergeCell ref="AD63:AE63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="T64:U64"/>
-    <mergeCell ref="V64:W64"/>
-    <mergeCell ref="X64:Y64"/>
-    <mergeCell ref="Z64:AA64"/>
-    <mergeCell ref="AB64:AC64"/>
-    <mergeCell ref="AD64:AE64"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="V61:W61"/>
-    <mergeCell ref="X61:Y61"/>
-    <mergeCell ref="Z61:AA61"/>
-    <mergeCell ref="AB61:AC61"/>
-    <mergeCell ref="AD61:AE61"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="V62:W62"/>
-    <mergeCell ref="X62:Y62"/>
-    <mergeCell ref="Z62:AA62"/>
-    <mergeCell ref="AB62:AC62"/>
-    <mergeCell ref="AD62:AE62"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="V67:W67"/>
-    <mergeCell ref="X67:Y67"/>
-    <mergeCell ref="Z67:AA67"/>
-    <mergeCell ref="AB67:AC67"/>
-    <mergeCell ref="AD67:AE67"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="X68:Y68"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AB68:AC68"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="R65:S65"/>
-    <mergeCell ref="T65:U65"/>
-    <mergeCell ref="V65:W65"/>
-    <mergeCell ref="X65:Y65"/>
-    <mergeCell ref="Z65:AA65"/>
-    <mergeCell ref="AB65:AC65"/>
-    <mergeCell ref="AD65:AE65"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="T66:U66"/>
-    <mergeCell ref="V66:W66"/>
-    <mergeCell ref="X66:Y66"/>
-    <mergeCell ref="Z66:AA66"/>
-    <mergeCell ref="AB66:AC66"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="T71:U71"/>
-    <mergeCell ref="V71:W71"/>
-    <mergeCell ref="X71:Y71"/>
-    <mergeCell ref="Z71:AA71"/>
-    <mergeCell ref="AB71:AC71"/>
-    <mergeCell ref="AD71:AE71"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T72:U72"/>
-    <mergeCell ref="V72:W72"/>
-    <mergeCell ref="X72:Y72"/>
-    <mergeCell ref="Z72:AA72"/>
-    <mergeCell ref="AB72:AC72"/>
-    <mergeCell ref="AD72:AE72"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="V69:W69"/>
-    <mergeCell ref="X69:Y69"/>
-    <mergeCell ref="Z69:AA69"/>
-    <mergeCell ref="AB69:AC69"/>
-    <mergeCell ref="AD69:AE69"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="V70:W70"/>
-    <mergeCell ref="X70:Y70"/>
-    <mergeCell ref="Z70:AA70"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AD70:AE70"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="V75:W75"/>
-    <mergeCell ref="X75:Y75"/>
-    <mergeCell ref="Z75:AA75"/>
-    <mergeCell ref="AB75:AC75"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="V76:W76"/>
-    <mergeCell ref="X76:Y76"/>
-    <mergeCell ref="Z76:AA76"/>
-    <mergeCell ref="AB76:AC76"/>
-    <mergeCell ref="AD76:AE76"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="V73:W73"/>
-    <mergeCell ref="X73:Y73"/>
-    <mergeCell ref="Z73:AA73"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AD73:AE73"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="T74:U74"/>
-    <mergeCell ref="V74:W74"/>
-    <mergeCell ref="X74:Y74"/>
-    <mergeCell ref="Z74:AA74"/>
-    <mergeCell ref="AB74:AC74"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="R79:S79"/>
-    <mergeCell ref="T79:U79"/>
-    <mergeCell ref="V79:W79"/>
-    <mergeCell ref="X79:Y79"/>
-    <mergeCell ref="Z79:AA79"/>
-    <mergeCell ref="AB79:AC79"/>
-    <mergeCell ref="AD79:AE79"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="T80:U80"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="X80:Y80"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="AB80:AC80"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="V77:W77"/>
-    <mergeCell ref="X77:Y77"/>
-    <mergeCell ref="Z77:AA77"/>
-    <mergeCell ref="AB77:AC77"/>
-    <mergeCell ref="AD77:AE77"/>
-    <mergeCell ref="R78:S78"/>
-    <mergeCell ref="T78:U78"/>
-    <mergeCell ref="V78:W78"/>
-    <mergeCell ref="X78:Y78"/>
-    <mergeCell ref="Z78:AA78"/>
-    <mergeCell ref="AB78:AC78"/>
-    <mergeCell ref="AD78:AE78"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="T83:U83"/>
-    <mergeCell ref="V83:W83"/>
-    <mergeCell ref="X83:Y83"/>
-    <mergeCell ref="Z83:AA83"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AD83:AE83"/>
-    <mergeCell ref="R84:S84"/>
-    <mergeCell ref="T84:U84"/>
-    <mergeCell ref="V84:W84"/>
-    <mergeCell ref="X84:Y84"/>
-    <mergeCell ref="Z84:AA84"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AD84:AE84"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="T81:U81"/>
-    <mergeCell ref="V81:W81"/>
-    <mergeCell ref="X81:Y81"/>
-    <mergeCell ref="Z81:AA81"/>
-    <mergeCell ref="AB81:AC81"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="R82:S82"/>
-    <mergeCell ref="T82:U82"/>
-    <mergeCell ref="V82:W82"/>
-    <mergeCell ref="X82:Y82"/>
-    <mergeCell ref="Z82:AA82"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AD82:AE82"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="T87:U87"/>
-    <mergeCell ref="V87:W87"/>
-    <mergeCell ref="X87:Y87"/>
-    <mergeCell ref="Z87:AA87"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="R88:S88"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="V88:W88"/>
-    <mergeCell ref="X88:Y88"/>
-    <mergeCell ref="Z88:AA88"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AD88:AE88"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="T85:U85"/>
-    <mergeCell ref="V85:W85"/>
-    <mergeCell ref="X85:Y85"/>
-    <mergeCell ref="Z85:AA85"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AD85:AE85"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="T86:U86"/>
-    <mergeCell ref="V86:W86"/>
-    <mergeCell ref="X86:Y86"/>
-    <mergeCell ref="Z86:AA86"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="R91:S91"/>
-    <mergeCell ref="T91:U91"/>
-    <mergeCell ref="V91:W91"/>
-    <mergeCell ref="X91:Y91"/>
-    <mergeCell ref="Z91:AA91"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AD91:AE91"/>
-    <mergeCell ref="R92:S92"/>
-    <mergeCell ref="T92:U92"/>
-    <mergeCell ref="V92:W92"/>
-    <mergeCell ref="X92:Y92"/>
-    <mergeCell ref="Z92:AA92"/>
-    <mergeCell ref="AB92:AC92"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="T89:U89"/>
-    <mergeCell ref="V89:W89"/>
-    <mergeCell ref="X89:Y89"/>
-    <mergeCell ref="Z89:AA89"/>
-    <mergeCell ref="AB89:AC89"/>
-    <mergeCell ref="AD89:AE89"/>
-    <mergeCell ref="R90:S90"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="V90:W90"/>
-    <mergeCell ref="X90:Y90"/>
-    <mergeCell ref="Z90:AA90"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AD90:AE90"/>
-    <mergeCell ref="R95:S95"/>
-    <mergeCell ref="T95:U95"/>
-    <mergeCell ref="V95:W95"/>
-    <mergeCell ref="X95:Y95"/>
-    <mergeCell ref="Z95:AA95"/>
-    <mergeCell ref="AB95:AC95"/>
-    <mergeCell ref="AD95:AE95"/>
-    <mergeCell ref="R96:S96"/>
-    <mergeCell ref="T96:U96"/>
-    <mergeCell ref="V96:W96"/>
-    <mergeCell ref="X96:Y96"/>
-    <mergeCell ref="Z96:AA96"/>
-    <mergeCell ref="AB96:AC96"/>
-    <mergeCell ref="AD96:AE96"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="T93:U93"/>
-    <mergeCell ref="V93:W93"/>
-    <mergeCell ref="X93:Y93"/>
-    <mergeCell ref="Z93:AA93"/>
-    <mergeCell ref="AB93:AC93"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="R94:S94"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="V94:W94"/>
-    <mergeCell ref="X94:Y94"/>
-    <mergeCell ref="Z94:AA94"/>
-    <mergeCell ref="AB94:AC94"/>
-    <mergeCell ref="AD94:AE94"/>
-    <mergeCell ref="R99:S99"/>
-    <mergeCell ref="T99:U99"/>
-    <mergeCell ref="V99:W99"/>
-    <mergeCell ref="X99:Y99"/>
-    <mergeCell ref="Z99:AA99"/>
-    <mergeCell ref="AB99:AC99"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="R100:S100"/>
-    <mergeCell ref="T100:U100"/>
-    <mergeCell ref="V100:W100"/>
-    <mergeCell ref="X100:Y100"/>
-    <mergeCell ref="Z100:AA100"/>
-    <mergeCell ref="AB100:AC100"/>
-    <mergeCell ref="AD100:AE100"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="T97:U97"/>
-    <mergeCell ref="V97:W97"/>
-    <mergeCell ref="X97:Y97"/>
-    <mergeCell ref="Z97:AA97"/>
-    <mergeCell ref="AB97:AC97"/>
-    <mergeCell ref="AD97:AE97"/>
-    <mergeCell ref="R98:S98"/>
-    <mergeCell ref="T98:U98"/>
-    <mergeCell ref="V98:W98"/>
-    <mergeCell ref="X98:Y98"/>
-    <mergeCell ref="Z98:AA98"/>
-    <mergeCell ref="AB98:AC98"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="R103:S103"/>
-    <mergeCell ref="T103:U103"/>
-    <mergeCell ref="V103:W103"/>
-    <mergeCell ref="X103:Y103"/>
-    <mergeCell ref="Z103:AA103"/>
-    <mergeCell ref="AB103:AC103"/>
-    <mergeCell ref="AD103:AE103"/>
-    <mergeCell ref="R104:S104"/>
-    <mergeCell ref="T104:U104"/>
-    <mergeCell ref="V104:W104"/>
-    <mergeCell ref="X104:Y104"/>
-    <mergeCell ref="Z104:AA104"/>
-    <mergeCell ref="AB104:AC104"/>
-    <mergeCell ref="AD104:AE104"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="T101:U101"/>
-    <mergeCell ref="V101:W101"/>
-    <mergeCell ref="X101:Y101"/>
-    <mergeCell ref="Z101:AA101"/>
-    <mergeCell ref="AB101:AC101"/>
-    <mergeCell ref="AD101:AE101"/>
-    <mergeCell ref="R102:S102"/>
-    <mergeCell ref="T102:U102"/>
-    <mergeCell ref="V102:W102"/>
-    <mergeCell ref="X102:Y102"/>
-    <mergeCell ref="Z102:AA102"/>
-    <mergeCell ref="AB102:AC102"/>
-    <mergeCell ref="AD102:AE102"/>
-    <mergeCell ref="R107:S107"/>
-    <mergeCell ref="T107:U107"/>
-    <mergeCell ref="V107:W107"/>
-    <mergeCell ref="X107:Y107"/>
-    <mergeCell ref="Z107:AA107"/>
-    <mergeCell ref="AB107:AC107"/>
-    <mergeCell ref="AD107:AE107"/>
-    <mergeCell ref="R108:S108"/>
-    <mergeCell ref="T108:U108"/>
-    <mergeCell ref="V108:W108"/>
-    <mergeCell ref="X108:Y108"/>
-    <mergeCell ref="Z108:AA108"/>
-    <mergeCell ref="AB108:AC108"/>
-    <mergeCell ref="AD108:AE108"/>
-    <mergeCell ref="R105:S105"/>
-    <mergeCell ref="T105:U105"/>
-    <mergeCell ref="V105:W105"/>
-    <mergeCell ref="X105:Y105"/>
-    <mergeCell ref="Z105:AA105"/>
-    <mergeCell ref="AB105:AC105"/>
-    <mergeCell ref="AD105:AE105"/>
-    <mergeCell ref="R106:S106"/>
-    <mergeCell ref="T106:U106"/>
-    <mergeCell ref="V106:W106"/>
-    <mergeCell ref="X106:Y106"/>
-    <mergeCell ref="Z106:AA106"/>
-    <mergeCell ref="AB106:AC106"/>
-    <mergeCell ref="AD106:AE106"/>
-    <mergeCell ref="R111:S111"/>
-    <mergeCell ref="T111:U111"/>
-    <mergeCell ref="V111:W111"/>
-    <mergeCell ref="X111:Y111"/>
-    <mergeCell ref="Z111:AA111"/>
-    <mergeCell ref="AB111:AC111"/>
-    <mergeCell ref="AD111:AE111"/>
-    <mergeCell ref="R112:S112"/>
-    <mergeCell ref="T112:U112"/>
-    <mergeCell ref="V112:W112"/>
-    <mergeCell ref="X112:Y112"/>
-    <mergeCell ref="Z112:AA112"/>
-    <mergeCell ref="AB112:AC112"/>
-    <mergeCell ref="AD112:AE112"/>
-    <mergeCell ref="R109:S109"/>
-    <mergeCell ref="T109:U109"/>
-    <mergeCell ref="V109:W109"/>
-    <mergeCell ref="X109:Y109"/>
-    <mergeCell ref="Z109:AA109"/>
-    <mergeCell ref="AB109:AC109"/>
-    <mergeCell ref="AD109:AE109"/>
-    <mergeCell ref="R110:S110"/>
-    <mergeCell ref="T110:U110"/>
-    <mergeCell ref="V110:W110"/>
-    <mergeCell ref="X110:Y110"/>
-    <mergeCell ref="Z110:AA110"/>
-    <mergeCell ref="AB110:AC110"/>
-    <mergeCell ref="AD110:AE110"/>
-    <mergeCell ref="R115:S115"/>
-    <mergeCell ref="T115:U115"/>
-    <mergeCell ref="V115:W115"/>
-    <mergeCell ref="X115:Y115"/>
-    <mergeCell ref="Z115:AA115"/>
-    <mergeCell ref="AB115:AC115"/>
-    <mergeCell ref="AD115:AE115"/>
-    <mergeCell ref="R116:S116"/>
-    <mergeCell ref="T116:U116"/>
-    <mergeCell ref="V116:W116"/>
-    <mergeCell ref="X116:Y116"/>
-    <mergeCell ref="Z116:AA116"/>
-    <mergeCell ref="AB116:AC116"/>
-    <mergeCell ref="AD116:AE116"/>
-    <mergeCell ref="R113:S113"/>
-    <mergeCell ref="T113:U113"/>
-    <mergeCell ref="V113:W113"/>
-    <mergeCell ref="X113:Y113"/>
-    <mergeCell ref="Z113:AA113"/>
-    <mergeCell ref="AB113:AC113"/>
-    <mergeCell ref="AD113:AE113"/>
-    <mergeCell ref="R114:S114"/>
-    <mergeCell ref="T114:U114"/>
-    <mergeCell ref="V114:W114"/>
-    <mergeCell ref="X114:Y114"/>
-    <mergeCell ref="Z114:AA114"/>
-    <mergeCell ref="AB114:AC114"/>
-    <mergeCell ref="AD114:AE114"/>
-    <mergeCell ref="R119:S119"/>
-    <mergeCell ref="T119:U119"/>
-    <mergeCell ref="V119:W119"/>
-    <mergeCell ref="X119:Y119"/>
-    <mergeCell ref="Z119:AA119"/>
-    <mergeCell ref="AB119:AC119"/>
-    <mergeCell ref="AD119:AE119"/>
-    <mergeCell ref="R120:S120"/>
-    <mergeCell ref="T120:U120"/>
-    <mergeCell ref="V120:W120"/>
-    <mergeCell ref="X120:Y120"/>
-    <mergeCell ref="Z120:AA120"/>
-    <mergeCell ref="AB120:AC120"/>
-    <mergeCell ref="AD120:AE120"/>
-    <mergeCell ref="R117:S117"/>
-    <mergeCell ref="T117:U117"/>
-    <mergeCell ref="V117:W117"/>
-    <mergeCell ref="X117:Y117"/>
-    <mergeCell ref="Z117:AA117"/>
-    <mergeCell ref="AB117:AC117"/>
-    <mergeCell ref="AD117:AE117"/>
-    <mergeCell ref="R118:S118"/>
-    <mergeCell ref="T118:U118"/>
-    <mergeCell ref="V118:W118"/>
-    <mergeCell ref="X118:Y118"/>
-    <mergeCell ref="Z118:AA118"/>
-    <mergeCell ref="AB118:AC118"/>
-    <mergeCell ref="AD118:AE118"/>
-    <mergeCell ref="R123:S123"/>
-    <mergeCell ref="T123:U123"/>
-    <mergeCell ref="V123:W123"/>
-    <mergeCell ref="X123:Y123"/>
-    <mergeCell ref="Z123:AA123"/>
-    <mergeCell ref="AB123:AC123"/>
-    <mergeCell ref="AD123:AE123"/>
-    <mergeCell ref="R124:S124"/>
-    <mergeCell ref="T124:U124"/>
-    <mergeCell ref="V124:W124"/>
-    <mergeCell ref="X124:Y124"/>
-    <mergeCell ref="Z124:AA124"/>
-    <mergeCell ref="AB124:AC124"/>
-    <mergeCell ref="AD124:AE124"/>
-    <mergeCell ref="R121:S121"/>
-    <mergeCell ref="T121:U121"/>
-    <mergeCell ref="V121:W121"/>
-    <mergeCell ref="X121:Y121"/>
-    <mergeCell ref="Z121:AA121"/>
-    <mergeCell ref="AB121:AC121"/>
-    <mergeCell ref="AD121:AE121"/>
-    <mergeCell ref="R122:S122"/>
-    <mergeCell ref="T122:U122"/>
-    <mergeCell ref="V122:W122"/>
-    <mergeCell ref="X122:Y122"/>
-    <mergeCell ref="Z122:AA122"/>
-    <mergeCell ref="AB122:AC122"/>
-    <mergeCell ref="AD122:AE122"/>
-    <mergeCell ref="R127:S127"/>
-    <mergeCell ref="T127:U127"/>
-    <mergeCell ref="V127:W127"/>
-    <mergeCell ref="X127:Y127"/>
-    <mergeCell ref="Z127:AA127"/>
-    <mergeCell ref="AB127:AC127"/>
-    <mergeCell ref="AD127:AE127"/>
-    <mergeCell ref="R128:S128"/>
-    <mergeCell ref="T128:U128"/>
-    <mergeCell ref="V128:W128"/>
-    <mergeCell ref="X128:Y128"/>
-    <mergeCell ref="Z128:AA128"/>
-    <mergeCell ref="AB128:AC128"/>
-    <mergeCell ref="AD128:AE128"/>
-    <mergeCell ref="R125:S125"/>
-    <mergeCell ref="T125:U125"/>
-    <mergeCell ref="V125:W125"/>
-    <mergeCell ref="X125:Y125"/>
-    <mergeCell ref="Z125:AA125"/>
-    <mergeCell ref="AB125:AC125"/>
-    <mergeCell ref="AD125:AE125"/>
-    <mergeCell ref="R126:S126"/>
-    <mergeCell ref="T126:U126"/>
-    <mergeCell ref="V126:W126"/>
-    <mergeCell ref="X126:Y126"/>
-    <mergeCell ref="Z126:AA126"/>
-    <mergeCell ref="AB126:AC126"/>
-    <mergeCell ref="AD126:AE126"/>
-    <mergeCell ref="R131:S131"/>
-    <mergeCell ref="T131:U131"/>
-    <mergeCell ref="V131:W131"/>
-    <mergeCell ref="X131:Y131"/>
-    <mergeCell ref="Z131:AA131"/>
-    <mergeCell ref="AB131:AC131"/>
-    <mergeCell ref="AD131:AE131"/>
-    <mergeCell ref="R132:S132"/>
-    <mergeCell ref="T132:U132"/>
-    <mergeCell ref="V132:W132"/>
-    <mergeCell ref="X132:Y132"/>
-    <mergeCell ref="Z132:AA132"/>
-    <mergeCell ref="AB132:AC132"/>
-    <mergeCell ref="AD132:AE132"/>
-    <mergeCell ref="R129:S129"/>
-    <mergeCell ref="T129:U129"/>
-    <mergeCell ref="V129:W129"/>
-    <mergeCell ref="X129:Y129"/>
-    <mergeCell ref="Z129:AA129"/>
-    <mergeCell ref="AB129:AC129"/>
-    <mergeCell ref="AD129:AE129"/>
-    <mergeCell ref="R130:S130"/>
-    <mergeCell ref="T130:U130"/>
-    <mergeCell ref="V130:W130"/>
-    <mergeCell ref="X130:Y130"/>
-    <mergeCell ref="Z130:AA130"/>
-    <mergeCell ref="AB130:AC130"/>
-    <mergeCell ref="AD130:AE130"/>
-    <mergeCell ref="R135:S135"/>
-    <mergeCell ref="T135:U135"/>
-    <mergeCell ref="V135:W135"/>
-    <mergeCell ref="X135:Y135"/>
-    <mergeCell ref="Z135:AA135"/>
-    <mergeCell ref="AB135:AC135"/>
-    <mergeCell ref="AD135:AE135"/>
-    <mergeCell ref="R136:S136"/>
-    <mergeCell ref="T136:U136"/>
-    <mergeCell ref="V136:W136"/>
-    <mergeCell ref="X136:Y136"/>
-    <mergeCell ref="Z136:AA136"/>
-    <mergeCell ref="AB136:AC136"/>
-    <mergeCell ref="AD136:AE136"/>
-    <mergeCell ref="R133:S133"/>
-    <mergeCell ref="T133:U133"/>
-    <mergeCell ref="V133:W133"/>
-    <mergeCell ref="X133:Y133"/>
-    <mergeCell ref="Z133:AA133"/>
-    <mergeCell ref="AB133:AC133"/>
-    <mergeCell ref="AD133:AE133"/>
-    <mergeCell ref="R134:S134"/>
-    <mergeCell ref="T134:U134"/>
-    <mergeCell ref="V134:W134"/>
-    <mergeCell ref="X134:Y134"/>
-    <mergeCell ref="Z134:AA134"/>
-    <mergeCell ref="AB134:AC134"/>
-    <mergeCell ref="AD134:AE134"/>
-    <mergeCell ref="R139:S139"/>
-    <mergeCell ref="T139:U139"/>
-    <mergeCell ref="V139:W139"/>
-    <mergeCell ref="X139:Y139"/>
-    <mergeCell ref="Z139:AA139"/>
-    <mergeCell ref="AB139:AC139"/>
-    <mergeCell ref="AD139:AE139"/>
-    <mergeCell ref="R140:S140"/>
-    <mergeCell ref="T140:U140"/>
-    <mergeCell ref="V140:W140"/>
-    <mergeCell ref="X140:Y140"/>
-    <mergeCell ref="Z140:AA140"/>
-    <mergeCell ref="AB140:AC140"/>
-    <mergeCell ref="AD140:AE140"/>
-    <mergeCell ref="R137:S137"/>
-    <mergeCell ref="T137:U137"/>
-    <mergeCell ref="V137:W137"/>
-    <mergeCell ref="X137:Y137"/>
-    <mergeCell ref="Z137:AA137"/>
-    <mergeCell ref="AB137:AC137"/>
-    <mergeCell ref="AD137:AE137"/>
-    <mergeCell ref="R138:S138"/>
-    <mergeCell ref="T138:U138"/>
-    <mergeCell ref="V138:W138"/>
-    <mergeCell ref="X138:Y138"/>
-    <mergeCell ref="Z138:AA138"/>
-    <mergeCell ref="AB138:AC138"/>
-    <mergeCell ref="AD138:AE138"/>
-    <mergeCell ref="R143:S143"/>
-    <mergeCell ref="T143:U143"/>
-    <mergeCell ref="V143:W143"/>
-    <mergeCell ref="X143:Y143"/>
-    <mergeCell ref="Z143:AA143"/>
-    <mergeCell ref="AB143:AC143"/>
-    <mergeCell ref="AD143:AE143"/>
-    <mergeCell ref="R144:S144"/>
-    <mergeCell ref="T144:U144"/>
-    <mergeCell ref="V144:W144"/>
-    <mergeCell ref="X144:Y144"/>
-    <mergeCell ref="Z144:AA144"/>
-    <mergeCell ref="AB144:AC144"/>
-    <mergeCell ref="AD144:AE144"/>
-    <mergeCell ref="R141:S141"/>
-    <mergeCell ref="T141:U141"/>
-    <mergeCell ref="V141:W141"/>
-    <mergeCell ref="X141:Y141"/>
-    <mergeCell ref="Z141:AA141"/>
-    <mergeCell ref="AB141:AC141"/>
-    <mergeCell ref="AD141:AE141"/>
-    <mergeCell ref="R142:S142"/>
-    <mergeCell ref="T142:U142"/>
-    <mergeCell ref="V142:W142"/>
-    <mergeCell ref="X142:Y142"/>
-    <mergeCell ref="Z142:AA142"/>
-    <mergeCell ref="AB142:AC142"/>
-    <mergeCell ref="AD142:AE142"/>
-    <mergeCell ref="R147:S147"/>
-    <mergeCell ref="T147:U147"/>
-    <mergeCell ref="V147:W147"/>
-    <mergeCell ref="X147:Y147"/>
-    <mergeCell ref="Z147:AA147"/>
-    <mergeCell ref="AB147:AC147"/>
-    <mergeCell ref="AD147:AE147"/>
-    <mergeCell ref="R148:S148"/>
-    <mergeCell ref="T148:U148"/>
-    <mergeCell ref="V148:W148"/>
-    <mergeCell ref="X148:Y148"/>
-    <mergeCell ref="Z148:AA148"/>
-    <mergeCell ref="AB148:AC148"/>
-    <mergeCell ref="AD148:AE148"/>
-    <mergeCell ref="R145:S145"/>
-    <mergeCell ref="T145:U145"/>
-    <mergeCell ref="V145:W145"/>
-    <mergeCell ref="X145:Y145"/>
-    <mergeCell ref="Z145:AA145"/>
-    <mergeCell ref="AB145:AC145"/>
-    <mergeCell ref="AD145:AE145"/>
-    <mergeCell ref="R146:S146"/>
-    <mergeCell ref="T146:U146"/>
-    <mergeCell ref="V146:W146"/>
-    <mergeCell ref="X146:Y146"/>
-    <mergeCell ref="Z146:AA146"/>
-    <mergeCell ref="AB146:AC146"/>
-    <mergeCell ref="AD146:AE146"/>
-    <mergeCell ref="R151:S151"/>
-    <mergeCell ref="T151:U151"/>
-    <mergeCell ref="V151:W151"/>
-    <mergeCell ref="X151:Y151"/>
-    <mergeCell ref="Z151:AA151"/>
-    <mergeCell ref="AB151:AC151"/>
-    <mergeCell ref="AD151:AE151"/>
-    <mergeCell ref="R152:S152"/>
-    <mergeCell ref="T152:U152"/>
-    <mergeCell ref="V152:W152"/>
-    <mergeCell ref="X152:Y152"/>
-    <mergeCell ref="Z152:AA152"/>
-    <mergeCell ref="AB152:AC152"/>
-    <mergeCell ref="AD152:AE152"/>
-    <mergeCell ref="R149:S149"/>
-    <mergeCell ref="T149:U149"/>
-    <mergeCell ref="V149:W149"/>
-    <mergeCell ref="X149:Y149"/>
-    <mergeCell ref="Z149:AA149"/>
-    <mergeCell ref="AB149:AC149"/>
-    <mergeCell ref="AD149:AE149"/>
-    <mergeCell ref="R150:S150"/>
-    <mergeCell ref="T150:U150"/>
-    <mergeCell ref="V150:W150"/>
-    <mergeCell ref="X150:Y150"/>
-    <mergeCell ref="Z150:AA150"/>
-    <mergeCell ref="AB150:AC150"/>
-    <mergeCell ref="AD150:AE150"/>
-    <mergeCell ref="R155:S155"/>
-    <mergeCell ref="T155:U155"/>
-    <mergeCell ref="V155:W155"/>
-    <mergeCell ref="X155:Y155"/>
-    <mergeCell ref="Z155:AA155"/>
-    <mergeCell ref="AB155:AC155"/>
-    <mergeCell ref="AD155:AE155"/>
-    <mergeCell ref="R156:S156"/>
-    <mergeCell ref="T156:U156"/>
-    <mergeCell ref="V156:W156"/>
-    <mergeCell ref="X156:Y156"/>
-    <mergeCell ref="Z156:AA156"/>
-    <mergeCell ref="AB156:AC156"/>
-    <mergeCell ref="AD156:AE156"/>
-    <mergeCell ref="R153:S153"/>
-    <mergeCell ref="T153:U153"/>
-    <mergeCell ref="V153:W153"/>
-    <mergeCell ref="X153:Y153"/>
-    <mergeCell ref="Z153:AA153"/>
-    <mergeCell ref="AB153:AC153"/>
-    <mergeCell ref="AD153:AE153"/>
-    <mergeCell ref="R154:S154"/>
-    <mergeCell ref="T154:U154"/>
-    <mergeCell ref="V154:W154"/>
-    <mergeCell ref="X154:Y154"/>
-    <mergeCell ref="Z154:AA154"/>
-    <mergeCell ref="AB154:AC154"/>
-    <mergeCell ref="AD154:AE154"/>
-    <mergeCell ref="R159:S159"/>
-    <mergeCell ref="T159:U159"/>
-    <mergeCell ref="V159:W159"/>
-    <mergeCell ref="X159:Y159"/>
-    <mergeCell ref="Z159:AA159"/>
-    <mergeCell ref="AB159:AC159"/>
-    <mergeCell ref="AD159:AE159"/>
-    <mergeCell ref="R160:S160"/>
-    <mergeCell ref="T160:U160"/>
-    <mergeCell ref="V160:W160"/>
-    <mergeCell ref="X160:Y160"/>
-    <mergeCell ref="Z160:AA160"/>
-    <mergeCell ref="AB160:AC160"/>
-    <mergeCell ref="AD160:AE160"/>
-    <mergeCell ref="R157:S157"/>
-    <mergeCell ref="T157:U157"/>
-    <mergeCell ref="V157:W157"/>
-    <mergeCell ref="X157:Y157"/>
-    <mergeCell ref="Z157:AA157"/>
-    <mergeCell ref="AB157:AC157"/>
-    <mergeCell ref="AD157:AE157"/>
-    <mergeCell ref="R158:S158"/>
-    <mergeCell ref="T158:U158"/>
-    <mergeCell ref="V158:W158"/>
-    <mergeCell ref="X158:Y158"/>
-    <mergeCell ref="Z158:AA158"/>
-    <mergeCell ref="AB158:AC158"/>
-    <mergeCell ref="AD158:AE158"/>
-    <mergeCell ref="R163:S163"/>
-    <mergeCell ref="T163:U163"/>
-    <mergeCell ref="V163:W163"/>
-    <mergeCell ref="X163:Y163"/>
-    <mergeCell ref="Z163:AA163"/>
-    <mergeCell ref="AB163:AC163"/>
-    <mergeCell ref="AD163:AE163"/>
-    <mergeCell ref="R164:S164"/>
-    <mergeCell ref="T164:U164"/>
-    <mergeCell ref="V164:W164"/>
-    <mergeCell ref="X164:Y164"/>
-    <mergeCell ref="Z164:AA164"/>
-    <mergeCell ref="AB164:AC164"/>
-    <mergeCell ref="AD164:AE164"/>
-    <mergeCell ref="R161:S161"/>
-    <mergeCell ref="T161:U161"/>
-    <mergeCell ref="V161:W161"/>
-    <mergeCell ref="X161:Y161"/>
-    <mergeCell ref="Z161:AA161"/>
-    <mergeCell ref="AB161:AC161"/>
-    <mergeCell ref="AD161:AE161"/>
-    <mergeCell ref="R162:S162"/>
-    <mergeCell ref="T162:U162"/>
-    <mergeCell ref="V162:W162"/>
-    <mergeCell ref="X162:Y162"/>
-    <mergeCell ref="Z162:AA162"/>
-    <mergeCell ref="AB162:AC162"/>
-    <mergeCell ref="AD162:AE162"/>
-    <mergeCell ref="R167:S167"/>
-    <mergeCell ref="T167:U167"/>
-    <mergeCell ref="V167:W167"/>
-    <mergeCell ref="X167:Y167"/>
-    <mergeCell ref="Z167:AA167"/>
-    <mergeCell ref="AB167:AC167"/>
-    <mergeCell ref="AD167:AE167"/>
-    <mergeCell ref="R168:S168"/>
-    <mergeCell ref="T168:U168"/>
-    <mergeCell ref="V168:W168"/>
-    <mergeCell ref="X168:Y168"/>
-    <mergeCell ref="Z168:AA168"/>
-    <mergeCell ref="AB168:AC168"/>
-    <mergeCell ref="AD168:AE168"/>
-    <mergeCell ref="R165:S165"/>
-    <mergeCell ref="T165:U165"/>
-    <mergeCell ref="V165:W165"/>
-    <mergeCell ref="X165:Y165"/>
-    <mergeCell ref="Z165:AA165"/>
-    <mergeCell ref="AB165:AC165"/>
-    <mergeCell ref="AD165:AE165"/>
-    <mergeCell ref="R166:S166"/>
-    <mergeCell ref="T166:U166"/>
-    <mergeCell ref="V166:W166"/>
-    <mergeCell ref="X166:Y166"/>
-    <mergeCell ref="Z166:AA166"/>
-    <mergeCell ref="AB166:AC166"/>
-    <mergeCell ref="AD166:AE166"/>
-    <mergeCell ref="R171:S171"/>
-    <mergeCell ref="T171:U171"/>
-    <mergeCell ref="V171:W171"/>
-    <mergeCell ref="X171:Y171"/>
-    <mergeCell ref="Z171:AA171"/>
-    <mergeCell ref="AB171:AC171"/>
-    <mergeCell ref="AD171:AE171"/>
-    <mergeCell ref="R172:S172"/>
-    <mergeCell ref="T172:U172"/>
-    <mergeCell ref="V172:W172"/>
-    <mergeCell ref="X172:Y172"/>
-    <mergeCell ref="Z172:AA172"/>
-    <mergeCell ref="AB172:AC172"/>
-    <mergeCell ref="AD172:AE172"/>
-    <mergeCell ref="R169:S169"/>
-    <mergeCell ref="T169:U169"/>
-    <mergeCell ref="V169:W169"/>
-    <mergeCell ref="X169:Y169"/>
-    <mergeCell ref="Z169:AA169"/>
-    <mergeCell ref="AB169:AC169"/>
-    <mergeCell ref="AD169:AE169"/>
-    <mergeCell ref="R170:S170"/>
-    <mergeCell ref="T170:U170"/>
-    <mergeCell ref="V170:W170"/>
-    <mergeCell ref="X170:Y170"/>
-    <mergeCell ref="Z170:AA170"/>
-    <mergeCell ref="AB170:AC170"/>
-    <mergeCell ref="AD170:AE170"/>
-    <mergeCell ref="R175:S175"/>
-    <mergeCell ref="T175:U175"/>
-    <mergeCell ref="V175:W175"/>
-    <mergeCell ref="X175:Y175"/>
-    <mergeCell ref="Z175:AA175"/>
-    <mergeCell ref="AB175:AC175"/>
-    <mergeCell ref="AD175:AE175"/>
-    <mergeCell ref="R176:S176"/>
-    <mergeCell ref="T176:U176"/>
-    <mergeCell ref="V176:W176"/>
-    <mergeCell ref="X176:Y176"/>
-    <mergeCell ref="Z176:AA176"/>
-    <mergeCell ref="AB176:AC176"/>
-    <mergeCell ref="AD176:AE176"/>
-    <mergeCell ref="R173:S173"/>
-    <mergeCell ref="T173:U173"/>
-    <mergeCell ref="V173:W173"/>
-    <mergeCell ref="X173:Y173"/>
-    <mergeCell ref="Z173:AA173"/>
-    <mergeCell ref="AB173:AC173"/>
-    <mergeCell ref="AD173:AE173"/>
-    <mergeCell ref="R174:S174"/>
-    <mergeCell ref="T174:U174"/>
-    <mergeCell ref="V174:W174"/>
-    <mergeCell ref="X174:Y174"/>
-    <mergeCell ref="Z174:AA174"/>
-    <mergeCell ref="AB174:AC174"/>
-    <mergeCell ref="AD174:AE174"/>
-    <mergeCell ref="R179:S179"/>
-    <mergeCell ref="T179:U179"/>
-    <mergeCell ref="V179:W179"/>
-    <mergeCell ref="X179:Y179"/>
-    <mergeCell ref="Z179:AA179"/>
-    <mergeCell ref="AB179:AC179"/>
-    <mergeCell ref="AD179:AE179"/>
-    <mergeCell ref="R180:S180"/>
-    <mergeCell ref="T180:U180"/>
-    <mergeCell ref="V180:W180"/>
-    <mergeCell ref="X180:Y180"/>
-    <mergeCell ref="Z180:AA180"/>
-    <mergeCell ref="AB180:AC180"/>
-    <mergeCell ref="AD180:AE180"/>
-    <mergeCell ref="R177:S177"/>
-    <mergeCell ref="T177:U177"/>
-    <mergeCell ref="V177:W177"/>
-    <mergeCell ref="X177:Y177"/>
-    <mergeCell ref="Z177:AA177"/>
-    <mergeCell ref="AB177:AC177"/>
-    <mergeCell ref="AD177:AE177"/>
-    <mergeCell ref="R178:S178"/>
-    <mergeCell ref="T178:U178"/>
-    <mergeCell ref="V178:W178"/>
-    <mergeCell ref="X178:Y178"/>
-    <mergeCell ref="Z178:AA178"/>
-    <mergeCell ref="AB178:AC178"/>
-    <mergeCell ref="AD178:AE178"/>
-    <mergeCell ref="R183:S183"/>
-    <mergeCell ref="T183:U183"/>
-    <mergeCell ref="V183:W183"/>
-    <mergeCell ref="X183:Y183"/>
-    <mergeCell ref="Z183:AA183"/>
-    <mergeCell ref="AB183:AC183"/>
-    <mergeCell ref="AD183:AE183"/>
-    <mergeCell ref="R181:S181"/>
-    <mergeCell ref="T181:U181"/>
-    <mergeCell ref="V181:W181"/>
-    <mergeCell ref="X181:Y181"/>
-    <mergeCell ref="Z181:AA181"/>
-    <mergeCell ref="AB181:AC181"/>
-    <mergeCell ref="AD181:AE181"/>
-    <mergeCell ref="R182:S182"/>
-    <mergeCell ref="T182:U182"/>
-    <mergeCell ref="V182:W182"/>
-    <mergeCell ref="X182:Y182"/>
-    <mergeCell ref="Z182:AA182"/>
-    <mergeCell ref="AB182:AC182"/>
-    <mergeCell ref="AD182:AE182"/>
-    <mergeCell ref="R186:S186"/>
-    <mergeCell ref="T186:U186"/>
-    <mergeCell ref="V186:W186"/>
-    <mergeCell ref="X186:Y186"/>
-    <mergeCell ref="Z186:AA186"/>
-    <mergeCell ref="AB186:AC186"/>
-    <mergeCell ref="AD186:AE186"/>
-    <mergeCell ref="R184:S184"/>
-    <mergeCell ref="T184:U184"/>
-    <mergeCell ref="V184:W184"/>
-    <mergeCell ref="X184:Y184"/>
-    <mergeCell ref="Z184:AA184"/>
-    <mergeCell ref="AB184:AC184"/>
-    <mergeCell ref="AD184:AE184"/>
-    <mergeCell ref="R185:S185"/>
-    <mergeCell ref="T185:U185"/>
-    <mergeCell ref="V185:W185"/>
-    <mergeCell ref="X185:Y185"/>
-    <mergeCell ref="Z185:AA185"/>
-    <mergeCell ref="AB185:AC185"/>
-    <mergeCell ref="AD185:AE185"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="Z9:AA10"/>
-    <mergeCell ref="X9:Y10"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="T9:U10"/>
-    <mergeCell ref="AD14:AE14"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="AD9:AE10"/>
-    <mergeCell ref="AB9:AC10"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="Z35:AA35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AB34:AC34"/>
+    <mergeCell ref="AB33:AC33"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="AB31:AC31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="AB39:AC39"/>
+    <mergeCell ref="AB40:AC40"/>
+    <mergeCell ref="Z40:AA40"/>
+    <mergeCell ref="AB37:AC37"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="AI8:AI10"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="AH8:AH10"/>
+    <mergeCell ref="AF8:AF10"/>
+    <mergeCell ref="AB30:AC30"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="AB29:AC29"/>
+    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="AB27:AC27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="20000" scale="17" fitToHeight="0" orientation="portrait" r:id="rId1"/>
